--- a/assets/score-sheets/19 Chicagoland 2026 Fantasy League Results.xlsx
+++ b/assets/score-sheets/19 Chicagoland 2026 Fantasy League Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://houcks-my.sharepoint.com/personal/michael_gehman_houcks_com/Documents/Desktop/NASCAR League/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="8_{CAFF266D-6030-4ED5-B5CE-95E1A19659D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DED9F114-1B8F-437A-8C7E-4FF1741142C6}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="8_{CAFF266D-6030-4ED5-B5CE-95E1A19659D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{291D777B-06BA-4984-A390-1CBC87F47E9A}"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="180" windowWidth="21600" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35085" yWindow="360" windowWidth="21600" windowHeight="13950" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Drivers" sheetId="21" r:id="rId1"/>
@@ -1287,6 +1287,66 @@
     <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="68"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="68"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="68"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="68"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="68"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="68"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1335,19 +1395,7 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="68"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="68"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="68"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="68"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="68"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1365,20 +1413,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="68"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="68"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="68"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -1441,42 +1477,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1712,25 +1712,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
-                  <c:v>1272</c:v>
+                  <c:v>1294</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>847</c:v>
+                  <c:v>885</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>977</c:v>
+                  <c:v>1045</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>883</c:v>
+                  <c:v>953</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1322</c:v>
+                  <c:v>1387</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>863</c:v>
+                  <c:v>924</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>913</c:v>
+                  <c:v>963</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -2149,28 +2149,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
-                  <c:v>872</c:v>
+                  <c:v>922</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>977</c:v>
+                  <c:v>1045</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>991</c:v>
+                  <c:v>1041</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1027</c:v>
+                  <c:v>1106</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1182</c:v>
+                  <c:v>1226</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>559</c:v>
+                  <c:v>609</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>941</c:v>
+                  <c:v>1036</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>1272</c:v>
+                  <c:v>1294</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>0</c:v>
@@ -2584,25 +2584,25 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="30"/>
                 <c:pt idx="0">
-                  <c:v>1272</c:v>
+                  <c:v>1294</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>868</c:v>
+                  <c:v>968</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1045</c:v>
+                  <c:v>1098</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1123</c:v>
+                  <c:v>1147</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>672</c:v>
+                  <c:v>722</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>910</c:v>
+                  <c:v>989</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>976</c:v>
+                  <c:v>1041</c:v>
                 </c:pt>
                 <c:pt idx="21">
                   <c:v>0</c:v>
@@ -5012,219 +5012,219 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="110" t="s">
+      <c r="B1" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="97" t="s">
+      <c r="C1" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="100" t="s">
+      <c r="D1" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="E1" s="97" t="s">
+      <c r="E1" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="F1" s="100" t="s">
+      <c r="F1" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="G1" s="97" t="s">
+      <c r="G1" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="H1" s="100" t="s">
+      <c r="H1" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="97" t="s">
+      <c r="I1" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="100" t="s">
+      <c r="J1" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="97" t="s">
+      <c r="K1" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="M1" s="97" t="s">
+      <c r="L1" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="M1" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="N1" s="97" t="s">
+      <c r="N1" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="O1" s="97" t="s">
+      <c r="O1" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="97" t="s">
+      <c r="P1" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="Q1" s="97" t="s">
+      <c r="Q1" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="R1" s="97" t="s">
+      <c r="R1" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="97" t="s">
+      <c r="S1" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="97" t="s">
+      <c r="T1" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="U1" s="97" t="s">
+      <c r="U1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="V1" s="97" t="s">
+      <c r="V1" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="W1" s="97" t="s">
+      <c r="W1" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="97" t="s">
+      <c r="X1" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="97" t="s">
+      <c r="Y1" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="Z1" s="97" t="s">
+      <c r="Z1" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="AA1" s="97" t="s">
+      <c r="AA1" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="AB1" s="97" t="s">
+      <c r="AB1" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="AC1" s="100" t="s">
+      <c r="AC1" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="AD1" s="97" t="s">
+      <c r="AD1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="AE1" s="97" t="s">
+      <c r="AE1" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="AF1" s="97" t="s">
+      <c r="AF1" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="AG1" s="97" t="s">
+      <c r="AG1" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="AH1" s="97" t="s">
+      <c r="AH1" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="AI1" s="97" t="s">
+      <c r="AI1" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="AJ1" s="97" t="s">
+      <c r="AJ1" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="AK1" s="97" t="s">
+      <c r="AK1" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="AL1" s="107" t="s">
+      <c r="AL1" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="AM1" s="107" t="s">
+      <c r="AM1" s="91" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A2" s="111"/>
-      <c r="B2" s="111"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
-      <c r="W2" s="98"/>
-      <c r="X2" s="98"/>
-      <c r="Y2" s="98"/>
-      <c r="Z2" s="98"/>
-      <c r="AA2" s="98"/>
-      <c r="AB2" s="98"/>
-      <c r="AC2" s="101"/>
-      <c r="AD2" s="98"/>
-      <c r="AE2" s="98"/>
-      <c r="AF2" s="98"/>
-      <c r="AG2" s="98"/>
-      <c r="AH2" s="98"/>
-      <c r="AI2" s="98"/>
-      <c r="AJ2" s="98"/>
-      <c r="AK2" s="98"/>
-      <c r="AL2" s="108"/>
-      <c r="AM2" s="108"/>
-      <c r="AN2" s="136" t="s">
+      <c r="A2" s="90"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="88"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="88"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="88"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="88"/>
+      <c r="L2" s="85"/>
+      <c r="M2" s="88"/>
+      <c r="N2" s="88"/>
+      <c r="O2" s="88"/>
+      <c r="P2" s="88"/>
+      <c r="Q2" s="88"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="88"/>
+      <c r="T2" s="88"/>
+      <c r="U2" s="88"/>
+      <c r="V2" s="88"/>
+      <c r="W2" s="88"/>
+      <c r="X2" s="88"/>
+      <c r="Y2" s="88"/>
+      <c r="Z2" s="88"/>
+      <c r="AA2" s="88"/>
+      <c r="AB2" s="88"/>
+      <c r="AC2" s="85"/>
+      <c r="AD2" s="88"/>
+      <c r="AE2" s="88"/>
+      <c r="AF2" s="88"/>
+      <c r="AG2" s="88"/>
+      <c r="AH2" s="88"/>
+      <c r="AI2" s="88"/>
+      <c r="AJ2" s="88"/>
+      <c r="AK2" s="88"/>
+      <c r="AL2" s="92"/>
+      <c r="AM2" s="92"/>
+      <c r="AN2" s="86" t="s">
         <v>76</v>
       </c>
-      <c r="AO2" s="136"/>
+      <c r="AO2" s="86"/>
       <c r="AP2" s="63"/>
-      <c r="AQ2" s="136" t="s">
+      <c r="AQ2" s="86" t="s">
         <v>78</v>
       </c>
-      <c r="AR2" s="136"/>
+      <c r="AR2" s="86"/>
       <c r="AS2" s="63"/>
-      <c r="AT2" s="136" t="s">
+      <c r="AT2" s="86" t="s">
         <v>77</v>
       </c>
-      <c r="AU2" s="136"/>
+      <c r="AU2" s="86"/>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.35">
-      <c r="A3" s="111"/>
-      <c r="B3" s="111"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="101"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="98"/>
-      <c r="Q3" s="98"/>
-      <c r="R3" s="98"/>
-      <c r="S3" s="98"/>
-      <c r="T3" s="98"/>
-      <c r="U3" s="98"/>
-      <c r="V3" s="98"/>
-      <c r="W3" s="98"/>
-      <c r="X3" s="98"/>
-      <c r="Y3" s="98"/>
-      <c r="Z3" s="98"/>
-      <c r="AA3" s="98"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="101"/>
-      <c r="AD3" s="98"/>
-      <c r="AE3" s="98"/>
-      <c r="AF3" s="98"/>
-      <c r="AG3" s="98"/>
-      <c r="AH3" s="98"/>
-      <c r="AI3" s="98"/>
-      <c r="AJ3" s="98"/>
-      <c r="AK3" s="98"/>
-      <c r="AL3" s="108"/>
-      <c r="AM3" s="108"/>
+      <c r="A3" s="90"/>
+      <c r="B3" s="90"/>
+      <c r="C3" s="88"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="88"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="88"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="88"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="88"/>
+      <c r="P3" s="88"/>
+      <c r="Q3" s="88"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="88"/>
+      <c r="T3" s="88"/>
+      <c r="U3" s="88"/>
+      <c r="V3" s="88"/>
+      <c r="W3" s="88"/>
+      <c r="X3" s="88"/>
+      <c r="Y3" s="88"/>
+      <c r="Z3" s="88"/>
+      <c r="AA3" s="88"/>
+      <c r="AB3" s="88"/>
+      <c r="AC3" s="85"/>
+      <c r="AD3" s="88"/>
+      <c r="AE3" s="88"/>
+      <c r="AF3" s="88"/>
+      <c r="AG3" s="88"/>
+      <c r="AH3" s="88"/>
+      <c r="AI3" s="88"/>
+      <c r="AJ3" s="88"/>
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="92"/>
+      <c r="AM3" s="92"/>
       <c r="AN3" t="s">
         <v>18</v>
       </c>
@@ -5303,9 +5303,11 @@
         <v>33</v>
       </c>
       <c r="T4" s="61">
+        <v>29</v>
+      </c>
+      <c r="U4" s="61">
         <v>19</v>
       </c>
-      <c r="U4" s="61"/>
       <c r="V4" s="61"/>
       <c r="W4" s="61"/>
       <c r="X4" s="61"/>
@@ -5325,22 +5327,22 @@
       <c r="AL4" s="61"/>
       <c r="AM4" s="61">
         <f>SUM(C4:AL4)</f>
-        <v>346</v>
-      </c>
-      <c r="AN4" s="133" t="s">
+        <v>375</v>
+      </c>
+      <c r="AN4" s="81" t="s">
         <v>98</v>
       </c>
       <c r="AO4" s="71" t="s">
         <v>99</v>
       </c>
-      <c r="AQ4" s="133" t="s">
+      <c r="AQ4" s="81" t="s">
         <v>89</v>
       </c>
       <c r="AR4" s="71" t="s">
         <v>104</v>
       </c>
       <c r="AS4" s="65"/>
-      <c r="AT4" s="133" t="s">
+      <c r="AT4" s="81" t="s">
         <v>90</v>
       </c>
       <c r="AU4" s="71" t="s">
@@ -5406,9 +5408,11 @@
         <v>15</v>
       </c>
       <c r="T5" s="61">
+        <v>31</v>
+      </c>
+      <c r="U5" s="61">
         <v>33</v>
       </c>
-      <c r="U5" s="61"/>
       <c r="V5" s="61"/>
       <c r="W5" s="61"/>
       <c r="X5" s="61"/>
@@ -5428,18 +5432,18 @@
       <c r="AL5" s="61"/>
       <c r="AM5" s="61">
         <f t="shared" ref="AM5:AM46" si="0">SUM(C5:AL5)</f>
-        <v>402</v>
-      </c>
-      <c r="AN5" s="133"/>
+        <v>433</v>
+      </c>
+      <c r="AN5" s="81"/>
       <c r="AO5" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="AQ5" s="133"/>
+      <c r="AQ5" s="81"/>
       <c r="AR5" s="71" t="s">
         <v>105</v>
       </c>
       <c r="AS5" s="65"/>
-      <c r="AT5" s="133"/>
+      <c r="AT5" s="81"/>
       <c r="AU5" s="71" t="s">
         <v>100</v>
       </c>
@@ -5546,20 +5550,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN7" s="134" t="s">
+      <c r="AN7" s="82" t="s">
         <v>129</v>
       </c>
       <c r="AO7" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="AQ7" s="133" t="s">
+      <c r="AQ7" s="81" t="s">
         <v>110</v>
       </c>
       <c r="AR7" s="71" t="s">
         <v>102</v>
       </c>
       <c r="AS7" s="65"/>
-      <c r="AT7" s="133" t="s">
+      <c r="AT7" s="81" t="s">
         <v>92</v>
       </c>
       <c r="AU7" s="71" t="s">
@@ -5625,9 +5629,11 @@
         <v>42</v>
       </c>
       <c r="T8" s="61">
+        <v>35</v>
+      </c>
+      <c r="U8" s="61">
         <v>12</v>
       </c>
-      <c r="U8" s="61"/>
       <c r="V8" s="61"/>
       <c r="W8" s="61"/>
       <c r="X8" s="61"/>
@@ -5647,18 +5653,18 @@
       <c r="AL8" s="61"/>
       <c r="AM8" s="61">
         <f t="shared" si="0"/>
-        <v>523</v>
-      </c>
-      <c r="AN8" s="135"/>
+        <v>558</v>
+      </c>
+      <c r="AN8" s="83"/>
       <c r="AO8" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="AQ8" s="133"/>
+      <c r="AQ8" s="81"/>
       <c r="AR8" s="71" t="s">
         <v>103</v>
       </c>
       <c r="AS8" s="65"/>
-      <c r="AT8" s="133"/>
+      <c r="AT8" s="81"/>
       <c r="AU8" s="71" t="s">
         <v>117</v>
       </c>
@@ -5712,9 +5718,11 @@
         <v>3</v>
       </c>
       <c r="T9" s="61">
+        <v>22</v>
+      </c>
+      <c r="U9" s="61">
         <v>16</v>
       </c>
-      <c r="U9" s="61"/>
       <c r="V9" s="61"/>
       <c r="W9" s="61"/>
       <c r="X9" s="61"/>
@@ -5734,7 +5742,7 @@
       <c r="AL9" s="61"/>
       <c r="AM9" s="61">
         <f t="shared" si="0"/>
-        <v>243</v>
+        <v>265</v>
       </c>
       <c r="AN9" s="68"/>
       <c r="AO9" s="64"/>
@@ -5791,20 +5799,20 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN10" s="134" t="s">
+      <c r="AN10" s="82" t="s">
         <v>87</v>
       </c>
       <c r="AO10" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="AQ10" s="133" t="s">
+      <c r="AQ10" s="81" t="s">
         <v>111</v>
       </c>
       <c r="AR10" s="71" t="s">
         <v>109</v>
       </c>
       <c r="AS10" s="65"/>
-      <c r="AT10" s="133" t="s">
+      <c r="AT10" s="81" t="s">
         <v>93</v>
       </c>
       <c r="AU10" s="71" t="s">
@@ -5872,7 +5880,9 @@
       <c r="T11" s="61">
         <v>0</v>
       </c>
-      <c r="U11" s="61"/>
+      <c r="U11" s="61">
+        <v>0</v>
+      </c>
       <c r="V11" s="61"/>
       <c r="W11" s="61"/>
       <c r="X11" s="61"/>
@@ -5894,16 +5904,16 @@
         <f t="shared" si="0"/>
         <v>217</v>
       </c>
-      <c r="AN11" s="135"/>
+      <c r="AN11" s="83"/>
       <c r="AO11" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="AQ11" s="133"/>
+      <c r="AQ11" s="81"/>
       <c r="AR11" s="71" t="s">
         <v>113</v>
       </c>
       <c r="AS11" s="65"/>
-      <c r="AT11" s="133"/>
+      <c r="AT11" s="81"/>
       <c r="AU11" s="71" t="s">
         <v>103</v>
       </c>
@@ -5967,9 +5977,11 @@
         <v>25</v>
       </c>
       <c r="T12" s="61">
+        <v>20</v>
+      </c>
+      <c r="U12" s="61">
         <v>30</v>
       </c>
-      <c r="U12" s="61"/>
       <c r="V12" s="61"/>
       <c r="W12" s="61"/>
       <c r="X12" s="61"/>
@@ -5989,7 +6001,7 @@
       <c r="AL12" s="61"/>
       <c r="AM12" s="61">
         <f t="shared" si="0"/>
-        <v>554</v>
+        <v>574</v>
       </c>
       <c r="AN12" s="68"/>
       <c r="AO12" s="64"/>
@@ -6045,21 +6057,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN13" s="133" t="s">
+      <c r="AN13" s="81" t="s">
         <v>128</v>
       </c>
       <c r="AO13" s="71" t="s">
         <v>104</v>
       </c>
       <c r="AP13" s="65"/>
-      <c r="AQ13" s="133" t="s">
+      <c r="AQ13" s="81" t="s">
         <v>126</v>
       </c>
       <c r="AR13" s="71" t="s">
         <v>101</v>
       </c>
       <c r="AS13" s="65"/>
-      <c r="AT13" s="133" t="s">
+      <c r="AT13" s="81" t="s">
         <v>115</v>
       </c>
       <c r="AU13" s="71" t="s">
@@ -6125,9 +6137,11 @@
         <v>23</v>
       </c>
       <c r="T14" s="61">
+        <v>11</v>
+      </c>
+      <c r="U14" s="61">
         <v>45</v>
       </c>
-      <c r="U14" s="61"/>
       <c r="V14" s="61"/>
       <c r="W14" s="61"/>
       <c r="X14" s="61"/>
@@ -6147,19 +6161,19 @@
       <c r="AL14" s="61"/>
       <c r="AM14" s="61">
         <f t="shared" si="0"/>
-        <v>751</v>
-      </c>
-      <c r="AN14" s="133"/>
+        <v>762</v>
+      </c>
+      <c r="AN14" s="81"/>
       <c r="AO14" s="71" t="s">
         <v>124</v>
       </c>
       <c r="AP14" s="65"/>
-      <c r="AQ14" s="133"/>
+      <c r="AQ14" s="81"/>
       <c r="AR14" s="71" t="s">
         <v>107</v>
       </c>
       <c r="AS14" s="65"/>
-      <c r="AT14" s="133"/>
+      <c r="AT14" s="81"/>
       <c r="AU14" s="71" t="s">
         <v>105</v>
       </c>
@@ -6223,9 +6237,11 @@
         <v>44</v>
       </c>
       <c r="T15" s="61">
+        <v>32</v>
+      </c>
+      <c r="U15" s="61">
         <v>36</v>
       </c>
-      <c r="U15" s="61"/>
       <c r="V15" s="61"/>
       <c r="W15" s="61"/>
       <c r="X15" s="61"/>
@@ -6245,7 +6261,7 @@
       <c r="AL15" s="61"/>
       <c r="AM15" s="61">
         <f t="shared" si="0"/>
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="AN15" s="69"/>
       <c r="AO15" s="67"/>
@@ -6303,21 +6319,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN16" s="133" t="s">
+      <c r="AN16" s="81" t="s">
         <v>88</v>
       </c>
       <c r="AO16" s="71" t="s">
         <v>106</v>
       </c>
       <c r="AP16" s="65"/>
-      <c r="AQ16" s="133" t="s">
+      <c r="AQ16" s="81" t="s">
         <v>125</v>
       </c>
       <c r="AR16" s="71" t="s">
         <v>106</v>
       </c>
       <c r="AS16" s="65"/>
-      <c r="AT16" s="133" t="s">
+      <c r="AT16" s="81" t="s">
         <v>116</v>
       </c>
       <c r="AU16" s="71" t="s">
@@ -6371,17 +6387,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN17" s="133"/>
+      <c r="AN17" s="81"/>
       <c r="AO17" s="71" t="s">
         <v>107</v>
       </c>
       <c r="AP17" s="65"/>
-      <c r="AQ17" s="133"/>
+      <c r="AQ17" s="81"/>
       <c r="AR17" s="71" t="s">
         <v>124</v>
       </c>
       <c r="AS17" s="65"/>
-      <c r="AT17" s="133"/>
+      <c r="AT17" s="81"/>
       <c r="AU17" s="71" t="s">
         <v>60</v>
       </c>
@@ -6445,9 +6461,11 @@
         <v>39</v>
       </c>
       <c r="T18" s="61">
+        <v>18</v>
+      </c>
+      <c r="U18" s="61">
         <v>23</v>
       </c>
-      <c r="U18" s="61"/>
       <c r="V18" s="61"/>
       <c r="W18" s="61"/>
       <c r="X18" s="61"/>
@@ -6467,7 +6485,7 @@
       <c r="AL18" s="61"/>
       <c r="AM18" s="61">
         <f t="shared" si="0"/>
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="AN18" s="70"/>
       <c r="AO18" s="66"/>
@@ -6537,9 +6555,11 @@
         <v>20</v>
       </c>
       <c r="T19" s="61">
+        <v>37</v>
+      </c>
+      <c r="U19" s="61">
         <v>70</v>
       </c>
-      <c r="U19" s="61"/>
       <c r="V19" s="61"/>
       <c r="W19" s="61"/>
       <c r="X19" s="61"/>
@@ -6559,23 +6579,23 @@
       <c r="AL19" s="61"/>
       <c r="AM19" s="61">
         <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="AN19" s="133" t="s">
+        <v>537</v>
+      </c>
+      <c r="AN19" s="81" t="s">
         <v>133</v>
       </c>
       <c r="AO19" s="71" t="s">
         <v>108</v>
       </c>
       <c r="AP19" s="65"/>
-      <c r="AQ19" s="133" t="s">
+      <c r="AQ19" s="81" t="s">
         <v>91</v>
       </c>
       <c r="AR19" s="71" t="s">
         <v>114</v>
       </c>
       <c r="AS19" s="65"/>
-      <c r="AT19" s="133" t="s">
+      <c r="AT19" s="81" t="s">
         <v>127</v>
       </c>
       <c r="AU19" s="71" t="s">
@@ -6641,9 +6661,11 @@
         <v>1</v>
       </c>
       <c r="T20" s="61">
+        <v>50</v>
+      </c>
+      <c r="U20" s="61">
         <v>40</v>
       </c>
-      <c r="U20" s="61"/>
       <c r="V20" s="61"/>
       <c r="W20" s="61"/>
       <c r="X20" s="61"/>
@@ -6663,19 +6685,19 @@
       <c r="AL20" s="61"/>
       <c r="AM20" s="61">
         <f t="shared" si="0"/>
-        <v>455</v>
-      </c>
-      <c r="AN20" s="133"/>
+        <v>505</v>
+      </c>
+      <c r="AN20" s="81"/>
       <c r="AO20" s="71" t="s">
         <v>132</v>
       </c>
       <c r="AP20" s="65"/>
-      <c r="AQ20" s="133"/>
+      <c r="AQ20" s="81"/>
       <c r="AR20" s="71" t="s">
         <v>68</v>
       </c>
       <c r="AS20" s="65"/>
-      <c r="AT20" s="133"/>
+      <c r="AT20" s="81"/>
       <c r="AU20" s="71" t="s">
         <v>107</v>
       </c>
@@ -6795,9 +6817,11 @@
         <v>23</v>
       </c>
       <c r="T22" s="61">
+        <v>13</v>
+      </c>
+      <c r="U22" s="61">
         <v>25</v>
       </c>
-      <c r="U22" s="61"/>
       <c r="V22" s="61"/>
       <c r="W22" s="61"/>
       <c r="X22" s="61"/>
@@ -6817,23 +6841,23 @@
       <c r="AL22" s="61"/>
       <c r="AM22" s="61">
         <f t="shared" si="0"/>
-        <v>372</v>
-      </c>
-      <c r="AN22" s="133" t="s">
+        <v>385</v>
+      </c>
+      <c r="AN22" s="81" t="s">
         <v>123</v>
       </c>
       <c r="AO22" s="71" t="s">
         <v>109</v>
       </c>
       <c r="AP22" s="65"/>
-      <c r="AQ22" s="133" t="s">
+      <c r="AQ22" s="81" t="s">
         <v>131</v>
       </c>
       <c r="AR22" s="71" t="s">
         <v>108</v>
       </c>
       <c r="AS22" s="65"/>
-      <c r="AT22" s="133" t="s">
+      <c r="AT22" s="81" t="s">
         <v>130</v>
       </c>
       <c r="AU22" s="71" t="s">
@@ -6899,9 +6923,11 @@
         <v>35</v>
       </c>
       <c r="T23" s="61">
+        <v>15</v>
+      </c>
+      <c r="U23" s="61">
         <v>40</v>
       </c>
-      <c r="U23" s="61"/>
       <c r="V23" s="61"/>
       <c r="W23" s="61"/>
       <c r="X23" s="61"/>
@@ -6921,19 +6947,19 @@
       <c r="AL23" s="61"/>
       <c r="AM23" s="61">
         <f t="shared" si="0"/>
-        <v>468</v>
-      </c>
-      <c r="AN23" s="133"/>
+        <v>483</v>
+      </c>
+      <c r="AN23" s="81"/>
       <c r="AO23" s="71" t="s">
         <v>122</v>
       </c>
       <c r="AP23" s="65"/>
-      <c r="AQ23" s="133"/>
+      <c r="AQ23" s="81"/>
       <c r="AR23" s="71" t="s">
         <v>117</v>
       </c>
       <c r="AS23" s="65"/>
-      <c r="AT23" s="133"/>
+      <c r="AT23" s="81"/>
       <c r="AU23" s="71" t="s">
         <v>124</v>
       </c>
@@ -6997,9 +7023,11 @@
         <v>6</v>
       </c>
       <c r="T24" s="61">
+        <v>25</v>
+      </c>
+      <c r="U24" s="61">
         <v>53</v>
       </c>
-      <c r="U24" s="61"/>
       <c r="V24" s="61"/>
       <c r="W24" s="61"/>
       <c r="X24" s="61"/>
@@ -7019,7 +7047,7 @@
       <c r="AL24" s="61"/>
       <c r="AM24" s="61">
         <f t="shared" si="0"/>
-        <v>474</v>
+        <v>499</v>
       </c>
       <c r="AN24" s="70"/>
       <c r="AO24" s="66"/>
@@ -7077,21 +7105,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN25" s="133">
+      <c r="AN25" s="81">
         <v>8</v>
       </c>
       <c r="AO25" s="71" t="s">
         <v>81</v>
       </c>
       <c r="AP25" s="65"/>
-      <c r="AQ25" s="133" t="s">
+      <c r="AQ25" s="81" t="s">
         <v>112</v>
       </c>
       <c r="AR25" s="71" t="s">
         <v>99</v>
       </c>
       <c r="AS25" s="65"/>
-      <c r="AT25" s="133">
+      <c r="AT25" s="81">
         <v>8</v>
       </c>
       <c r="AU25" s="71" t="s">
@@ -7145,17 +7173,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN26" s="133"/>
+      <c r="AN26" s="81"/>
       <c r="AO26" s="71" t="s">
         <v>82</v>
       </c>
       <c r="AP26" s="65"/>
-      <c r="AQ26" s="133"/>
+      <c r="AQ26" s="81"/>
       <c r="AR26" s="71" t="s">
         <v>100</v>
       </c>
       <c r="AS26" s="65"/>
-      <c r="AT26" s="133"/>
+      <c r="AT26" s="81"/>
       <c r="AU26" s="71" t="s">
         <v>82</v>
       </c>
@@ -7263,21 +7291,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN28" s="133">
+      <c r="AN28" s="81">
         <v>9</v>
       </c>
       <c r="AO28" s="71" t="s">
         <v>81</v>
       </c>
       <c r="AP28" s="65"/>
-      <c r="AQ28" s="133">
+      <c r="AQ28" s="81">
         <v>9</v>
       </c>
       <c r="AR28" s="71" t="s">
         <v>81</v>
       </c>
       <c r="AS28" s="65"/>
-      <c r="AT28" s="133">
+      <c r="AT28" s="81">
         <v>9</v>
       </c>
       <c r="AU28" s="71" t="s">
@@ -7331,17 +7359,17 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN29" s="133"/>
+      <c r="AN29" s="81"/>
       <c r="AO29" s="71" t="s">
         <v>82</v>
       </c>
       <c r="AP29" s="65"/>
-      <c r="AQ29" s="133"/>
+      <c r="AQ29" s="81"/>
       <c r="AR29" s="71" t="s">
         <v>82</v>
       </c>
       <c r="AS29" s="65"/>
-      <c r="AT29" s="133"/>
+      <c r="AT29" s="81"/>
       <c r="AU29" s="71" t="s">
         <v>82</v>
       </c>
@@ -7449,21 +7477,21 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN31" s="133">
+      <c r="AN31" s="81">
         <v>10</v>
       </c>
       <c r="AO31" s="71" t="s">
         <v>81</v>
       </c>
       <c r="AP31" s="65"/>
-      <c r="AQ31" s="133">
+      <c r="AQ31" s="81">
         <v>10</v>
       </c>
       <c r="AR31" s="71" t="s">
         <v>81</v>
       </c>
       <c r="AS31" s="65"/>
-      <c r="AT31" s="133">
+      <c r="AT31" s="81">
         <v>10</v>
       </c>
       <c r="AU31" s="71" t="s">
@@ -7529,9 +7557,11 @@
         <v>17</v>
       </c>
       <c r="T32" s="61">
+        <v>17</v>
+      </c>
+      <c r="U32" s="61">
         <v>22</v>
       </c>
-      <c r="U32" s="61"/>
       <c r="V32" s="61"/>
       <c r="W32" s="61"/>
       <c r="X32" s="61"/>
@@ -7551,19 +7581,19 @@
       <c r="AL32" s="61"/>
       <c r="AM32" s="61">
         <f t="shared" si="0"/>
-        <v>394</v>
-      </c>
-      <c r="AN32" s="133"/>
+        <v>411</v>
+      </c>
+      <c r="AN32" s="81"/>
       <c r="AO32" s="71" t="s">
         <v>82</v>
       </c>
       <c r="AP32" s="65"/>
-      <c r="AQ32" s="133"/>
+      <c r="AQ32" s="81"/>
       <c r="AR32" s="71" t="s">
         <v>82</v>
       </c>
       <c r="AS32" s="65"/>
-      <c r="AT32" s="133"/>
+      <c r="AT32" s="81"/>
       <c r="AU32" s="71" t="s">
         <v>82</v>
       </c>
@@ -7677,7 +7707,9 @@
       <c r="T34" s="61">
         <v>2</v>
       </c>
-      <c r="U34" s="61"/>
+      <c r="U34" s="61">
+        <v>2</v>
+      </c>
       <c r="V34" s="61"/>
       <c r="W34" s="61"/>
       <c r="X34" s="61"/>
@@ -7697,7 +7729,7 @@
       <c r="AL34" s="61"/>
       <c r="AM34" s="61">
         <f t="shared" si="0"/>
-        <v>718</v>
+        <v>720</v>
       </c>
     </row>
     <row r="35" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7747,8 +7779,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN35" s="139"/>
-      <c r="AO35" s="140"/>
+      <c r="AN35" s="95"/>
+      <c r="AO35" s="96"/>
     </row>
     <row r="36" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="75">
@@ -7809,9 +7841,11 @@
         <v>11</v>
       </c>
       <c r="T36" s="61">
+        <v>32</v>
+      </c>
+      <c r="U36" s="61">
         <v>35</v>
       </c>
-      <c r="U36" s="61"/>
       <c r="V36" s="61"/>
       <c r="W36" s="61"/>
       <c r="X36" s="61"/>
@@ -7831,10 +7865,10 @@
       <c r="AL36" s="61"/>
       <c r="AM36" s="61">
         <f t="shared" si="0"/>
-        <v>233</v>
-      </c>
-      <c r="AN36" s="141"/>
-      <c r="AO36" s="142"/>
+        <v>265</v>
+      </c>
+      <c r="AN36" s="97"/>
+      <c r="AO36" s="98"/>
     </row>
     <row r="37" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="75">
@@ -7883,8 +7917,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN37" s="141"/>
-      <c r="AO37" s="142"/>
+      <c r="AN37" s="97"/>
+      <c r="AO37" s="98"/>
     </row>
     <row r="38" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="75">
@@ -7933,8 +7967,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN38" s="141"/>
-      <c r="AO38" s="142"/>
+      <c r="AN38" s="97"/>
+      <c r="AO38" s="98"/>
     </row>
     <row r="39" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="75">
@@ -7995,9 +8029,11 @@
         <v>29</v>
       </c>
       <c r="T39" s="61">
+        <v>54</v>
+      </c>
+      <c r="U39" s="61">
         <v>38</v>
       </c>
-      <c r="U39" s="61"/>
       <c r="V39" s="61"/>
       <c r="W39" s="61"/>
       <c r="X39" s="61"/>
@@ -8017,10 +8053,10 @@
       <c r="AL39" s="61"/>
       <c r="AM39" s="61">
         <f t="shared" si="0"/>
-        <v>571</v>
-      </c>
-      <c r="AN39" s="143"/>
-      <c r="AO39" s="144"/>
+        <v>625</v>
+      </c>
+      <c r="AN39" s="99"/>
+      <c r="AO39" s="100"/>
     </row>
     <row r="40" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="75">
@@ -8069,8 +8105,8 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AN40" s="137"/>
-      <c r="AO40" s="138"/>
+      <c r="AN40" s="93"/>
+      <c r="AO40" s="94"/>
     </row>
     <row r="41" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="75">
@@ -8173,9 +8209,11 @@
         <v>27</v>
       </c>
       <c r="T42" s="61">
+        <v>33</v>
+      </c>
+      <c r="U42" s="61">
         <v>15</v>
       </c>
-      <c r="U42" s="61"/>
       <c r="V42" s="61"/>
       <c r="W42" s="61"/>
       <c r="X42" s="61"/>
@@ -8195,7 +8233,7 @@
       <c r="AL42" s="61"/>
       <c r="AM42" s="61">
         <f t="shared" si="0"/>
-        <v>409</v>
+        <v>442</v>
       </c>
     </row>
     <row r="43" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8353,9 +8391,11 @@
         <v>3</v>
       </c>
       <c r="T45" s="61">
+        <v>33</v>
+      </c>
+      <c r="U45" s="61">
         <v>1</v>
       </c>
-      <c r="U45" s="61"/>
       <c r="V45" s="61"/>
       <c r="W45" s="61"/>
       <c r="X45" s="61"/>
@@ -8375,7 +8415,7 @@
       <c r="AL45" s="61"/>
       <c r="AM45" s="61">
         <f t="shared" si="0"/>
-        <v>165</v>
+        <v>198</v>
       </c>
     </row>
     <row r="46" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -8437,9 +8477,11 @@
         <v>1</v>
       </c>
       <c r="T46" s="61">
+        <v>63</v>
+      </c>
+      <c r="U46" s="61">
         <v>12</v>
       </c>
-      <c r="U46" s="61"/>
       <c r="V46" s="61"/>
       <c r="W46" s="61"/>
       <c r="X46" s="61"/>
@@ -8459,7 +8501,7 @@
       <c r="AL46" s="61"/>
       <c r="AM46" s="61">
         <f t="shared" si="0"/>
-        <v>368</v>
+        <v>431</v>
       </c>
     </row>
     <row r="47" spans="1:41" ht="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -8571,355 +8613,355 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:56" ht="22" x14ac:dyDescent="0.25">
-      <c r="A1" s="81">
+      <c r="A1" s="101">
         <v>2025</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="81" t="s">
+      <c r="B1" s="102"/>
+      <c r="C1" s="101" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="82"/>
-      <c r="Y1" s="82"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="82"/>
-      <c r="AB1" s="82"/>
-      <c r="AC1" s="82"/>
-      <c r="AD1" s="82"/>
-      <c r="AE1" s="82"/>
-      <c r="AF1" s="82"/>
-      <c r="AG1" s="82"/>
-      <c r="AH1" s="82"/>
-      <c r="AI1" s="82"/>
-      <c r="AJ1" s="82"/>
-      <c r="AK1" s="82"/>
-      <c r="AL1" s="82"/>
-      <c r="AM1" s="82"/>
-      <c r="AN1" s="82"/>
-      <c r="AO1" s="82"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="102"/>
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="102"/>
+      <c r="AJ1" s="102"/>
+      <c r="AK1" s="102"/>
+      <c r="AL1" s="102"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
       <c r="AP1" s="48"/>
     </row>
     <row r="2" spans="1:56" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="83"/>
-      <c r="X2" s="83"/>
-      <c r="Y2" s="83"/>
-      <c r="Z2" s="83"/>
-      <c r="AA2" s="83"/>
-      <c r="AB2" s="83"/>
-      <c r="AC2" s="83"/>
-      <c r="AD2" s="83"/>
-      <c r="AE2" s="83"/>
-      <c r="AF2" s="83"/>
-      <c r="AG2" s="83"/>
-      <c r="AH2" s="83"/>
-      <c r="AI2" s="83"/>
-      <c r="AJ2" s="83"/>
-      <c r="AK2" s="83"/>
-      <c r="AL2" s="83"/>
-      <c r="AM2" s="83"/>
-      <c r="AN2" s="83"/>
-      <c r="AO2" s="83"/>
+      <c r="A2" s="103"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="103"/>
+      <c r="T2" s="103"/>
+      <c r="U2" s="103"/>
+      <c r="V2" s="103"/>
+      <c r="W2" s="103"/>
+      <c r="X2" s="103"/>
+      <c r="Y2" s="103"/>
+      <c r="Z2" s="103"/>
+      <c r="AA2" s="103"/>
+      <c r="AB2" s="103"/>
+      <c r="AC2" s="103"/>
+      <c r="AD2" s="103"/>
+      <c r="AE2" s="103"/>
+      <c r="AF2" s="103"/>
+      <c r="AG2" s="103"/>
+      <c r="AH2" s="103"/>
+      <c r="AI2" s="103"/>
+      <c r="AJ2" s="103"/>
+      <c r="AK2" s="103"/>
+      <c r="AL2" s="103"/>
+      <c r="AM2" s="103"/>
+      <c r="AN2" s="103"/>
+      <c r="AO2" s="103"/>
       <c r="AP2" s="48"/>
     </row>
     <row r="3" spans="1:56" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="D3" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="97" t="s">
+      <c r="E3" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="100" t="s">
+      <c r="F3" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="100" t="s">
+      <c r="H3" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="97" t="s">
+      <c r="I3" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="100" t="s">
+      <c r="J3" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="97" t="s">
+      <c r="K3" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="97" t="s">
+      <c r="L3" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="97" t="s">
+      <c r="N3" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="97" t="s">
+      <c r="O3" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="97" t="s">
+      <c r="P3" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="97" t="s">
+      <c r="Q3" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="97" t="s">
+      <c r="R3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="97" t="s">
+      <c r="S3" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="97" t="s">
+      <c r="T3" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="97" t="s">
+      <c r="U3" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="97" t="s">
+      <c r="V3" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="97" t="s">
+      <c r="W3" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="X3" s="97" t="s">
+      <c r="X3" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="Y3" s="97" t="s">
+      <c r="Y3" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="Z3" s="97" t="s">
+      <c r="Z3" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="AA3" s="97" t="s">
+      <c r="AA3" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="AB3" s="97" t="s">
+      <c r="AB3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="AC3" s="100" t="s">
+      <c r="AC3" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="AD3" s="97" t="s">
+      <c r="AD3" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="97" t="s">
+      <c r="AE3" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="AF3" s="97" t="s">
+      <c r="AF3" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="AG3" s="97" t="s">
+      <c r="AG3" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="AH3" s="97" t="s">
+      <c r="AH3" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="AI3" s="97" t="s">
+      <c r="AI3" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="AJ3" s="97" t="s">
+      <c r="AJ3" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="AK3" s="97" t="s">
+      <c r="AK3" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="AL3" s="107" t="s">
+      <c r="AL3" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="AM3" s="88" t="s">
+      <c r="AM3" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="AN3" s="91" t="s">
+      <c r="AN3" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="AO3" s="94" t="s">
+      <c r="AO3" s="114" t="s">
         <v>41</v>
       </c>
       <c r="AP3" s="47"/>
-      <c r="AQ3" s="104"/>
-      <c r="AR3" s="104"/>
-      <c r="AS3" s="104"/>
-      <c r="AT3" s="104"/>
-      <c r="AU3" s="104"/>
-      <c r="AV3" s="104"/>
-      <c r="AW3" s="104"/>
-      <c r="AX3" s="104"/>
-      <c r="AY3" s="104"/>
-      <c r="AZ3" s="104"/>
-      <c r="BA3" s="104"/>
-      <c r="BB3" s="104"/>
-      <c r="BC3" s="104"/>
-      <c r="BD3" s="104"/>
+      <c r="AQ3" s="120"/>
+      <c r="AR3" s="120"/>
+      <c r="AS3" s="120"/>
+      <c r="AT3" s="120"/>
+      <c r="AU3" s="120"/>
+      <c r="AV3" s="120"/>
+      <c r="AW3" s="120"/>
+      <c r="AX3" s="120"/>
+      <c r="AY3" s="120"/>
+      <c r="AZ3" s="120"/>
+      <c r="BA3" s="120"/>
+      <c r="BB3" s="120"/>
+      <c r="BC3" s="120"/>
+      <c r="BD3" s="120"/>
     </row>
     <row r="4" spans="1:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="114"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98"/>
-      <c r="W4" s="98"/>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="98"/>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="98"/>
-      <c r="AK4" s="98"/>
-      <c r="AL4" s="108"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="92"/>
-      <c r="AO4" s="95"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="W4" s="88"/>
+      <c r="X4" s="88"/>
+      <c r="Y4" s="88"/>
+      <c r="Z4" s="88"/>
+      <c r="AA4" s="88"/>
+      <c r="AB4" s="88"/>
+      <c r="AC4" s="85"/>
+      <c r="AD4" s="88"/>
+      <c r="AE4" s="88"/>
+      <c r="AF4" s="88"/>
+      <c r="AG4" s="88"/>
+      <c r="AH4" s="88"/>
+      <c r="AI4" s="88"/>
+      <c r="AJ4" s="88"/>
+      <c r="AK4" s="88"/>
+      <c r="AL4" s="92"/>
+      <c r="AM4" s="109"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="115"/>
       <c r="AP4" s="47"/>
-      <c r="AQ4" s="106"/>
-      <c r="AR4" s="105"/>
-      <c r="AS4" s="106"/>
-      <c r="AT4" s="105"/>
-      <c r="AU4" s="106"/>
-      <c r="AV4" s="105"/>
-      <c r="AW4" s="106"/>
-      <c r="AX4" s="105"/>
-      <c r="AY4" s="106"/>
-      <c r="AZ4" s="105"/>
-      <c r="BA4" s="106"/>
-      <c r="BB4" s="105"/>
-      <c r="BC4" s="106"/>
-      <c r="BD4" s="105"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="121"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="121"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="121"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="121"/>
+      <c r="BA4" s="122"/>
+      <c r="BB4" s="121"/>
+      <c r="BC4" s="122"/>
+      <c r="BD4" s="121"/>
     </row>
     <row r="5" spans="1:56" ht="11" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="115"/>
-      <c r="B5" s="112"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="99"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="99"/>
-      <c r="V5" s="99"/>
-      <c r="W5" s="99"/>
-      <c r="X5" s="99"/>
-      <c r="Y5" s="99"/>
-      <c r="Z5" s="99"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="99"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="99"/>
-      <c r="AF5" s="99"/>
-      <c r="AG5" s="99"/>
-      <c r="AH5" s="99"/>
-      <c r="AI5" s="99"/>
-      <c r="AJ5" s="99"/>
-      <c r="AK5" s="99"/>
-      <c r="AL5" s="109"/>
-      <c r="AM5" s="90"/>
-      <c r="AN5" s="93"/>
-      <c r="AO5" s="96"/>
+      <c r="A5" s="127"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="117"/>
+      <c r="W5" s="117"/>
+      <c r="X5" s="117"/>
+      <c r="Y5" s="117"/>
+      <c r="Z5" s="117"/>
+      <c r="AA5" s="117"/>
+      <c r="AB5" s="117"/>
+      <c r="AC5" s="118"/>
+      <c r="AD5" s="117"/>
+      <c r="AE5" s="117"/>
+      <c r="AF5" s="117"/>
+      <c r="AG5" s="117"/>
+      <c r="AH5" s="117"/>
+      <c r="AI5" s="117"/>
+      <c r="AJ5" s="117"/>
+      <c r="AK5" s="117"/>
+      <c r="AL5" s="123"/>
+      <c r="AM5" s="110"/>
+      <c r="AN5" s="113"/>
+      <c r="AO5" s="116"/>
       <c r="AP5" s="47"/>
-      <c r="AQ5" s="106"/>
-      <c r="AR5" s="105"/>
-      <c r="AS5" s="106"/>
-      <c r="AT5" s="105"/>
-      <c r="AU5" s="106"/>
-      <c r="AV5" s="105"/>
-      <c r="AW5" s="106"/>
-      <c r="AX5" s="105"/>
-      <c r="AY5" s="106"/>
-      <c r="AZ5" s="105"/>
-      <c r="BA5" s="106"/>
-      <c r="BB5" s="105"/>
-      <c r="BC5" s="106"/>
-      <c r="BD5" s="105"/>
+      <c r="AQ5" s="122"/>
+      <c r="AR5" s="121"/>
+      <c r="AS5" s="122"/>
+      <c r="AT5" s="121"/>
+      <c r="AU5" s="122"/>
+      <c r="AV5" s="121"/>
+      <c r="AW5" s="122"/>
+      <c r="AX5" s="121"/>
+      <c r="AY5" s="122"/>
+      <c r="AZ5" s="121"/>
+      <c r="BA5" s="122"/>
+      <c r="BB5" s="121"/>
+      <c r="BC5" s="122"/>
+      <c r="BD5" s="121"/>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="str">
+      <c r="A6" s="104" t="str">
         <f>Drivers!AN4</f>
         <v xml:space="preserve">Dehaven  </v>
       </c>
@@ -8997,11 +9039,11 @@
       </c>
       <c r="T6" s="25">
         <f>Drivers!T12</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="U6" s="25">
         <f>Drivers!U12</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V6" s="25">
         <f>Drivers!V12</f>
@@ -9071,21 +9113,21 @@
         <f>Drivers!AL12</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="116">
+      <c r="AM6" s="128">
         <f>SUM(C8:AL8)</f>
-        <v>1272</v>
-      </c>
-      <c r="AN6" s="123">
+        <v>1294</v>
+      </c>
+      <c r="AN6" s="135">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>2</v>
       </c>
-      <c r="AO6" s="129">
+      <c r="AO6" s="141">
         <f>AVERAGE(C8:AL8)</f>
-        <v>35.333333333333336</v>
+        <v>35.944444444444443</v>
       </c>
     </row>
     <row r="7" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="85"/>
+      <c r="A7" s="105"/>
       <c r="B7" s="49" t="str">
         <f>Drivers!AO5</f>
         <v>Reddick</v>
@@ -9164,7 +9206,7 @@
       </c>
       <c r="U7" s="26">
         <f>Drivers!U34</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" s="26">
         <f>Drivers!V34</f>
@@ -9234,9 +9276,9 @@
         <f>Drivers!AL34</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="117"/>
-      <c r="AN7" s="124"/>
-      <c r="AO7" s="130"/>
+      <c r="AM7" s="129"/>
+      <c r="AN7" s="136"/>
+      <c r="AO7" s="142"/>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2"/>
       <c r="AR7" s="2"/>
@@ -9254,7 +9296,7 @@
       <c r="BD7" s="2"/>
     </row>
     <row r="8" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="86"/>
+      <c r="A8" s="106"/>
       <c r="B8" s="49"/>
       <c r="C8" s="27">
         <f>SUM(C6+C7)</f>
@@ -9326,11 +9368,11 @@
       </c>
       <c r="T8" s="27">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="U8" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V8" s="27">
         <f t="shared" si="0"/>
@@ -9400,9 +9442,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM8" s="117"/>
-      <c r="AN8" s="124"/>
-      <c r="AO8" s="131"/>
+      <c r="AM8" s="129"/>
+      <c r="AN8" s="136"/>
+      <c r="AO8" s="143"/>
       <c r="AP8" s="13"/>
       <c r="AQ8" s="13"/>
       <c r="AR8" s="13"/>
@@ -9420,7 +9462,7 @@
       <c r="BD8" s="13"/>
     </row>
     <row r="9" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="87" t="str">
+      <c r="A9" s="107" t="str">
         <f>Drivers!AN7</f>
         <v>Gehman (1)</v>
       </c>
@@ -9498,11 +9540,11 @@
       </c>
       <c r="T9" s="38">
         <f>Drivers!T24</f>
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="U9" s="38">
         <f>Drivers!U24</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="V9" s="38">
         <f>Drivers!V24</f>
@@ -9572,17 +9614,17 @@
         <f>Drivers!AL24</f>
         <v>0</v>
       </c>
-      <c r="AM9" s="118">
+      <c r="AM9" s="130">
         <f>SUM(C11:AL11)</f>
-        <v>847</v>
-      </c>
-      <c r="AN9" s="125">
+        <v>885</v>
+      </c>
+      <c r="AN9" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>7</v>
       </c>
-      <c r="AO9" s="129">
+      <c r="AO9" s="141">
         <f t="shared" ref="AO9" si="1">AVERAGE(C11:AL11)</f>
-        <v>23.527777777777779</v>
+        <v>24.583333333333332</v>
       </c>
       <c r="AP9" s="2"/>
       <c r="AQ9" s="13"/>
@@ -9601,7 +9643,7 @@
       <c r="BD9" s="2"/>
     </row>
     <row r="10" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="85"/>
+      <c r="A10" s="105"/>
       <c r="B10" s="78" t="str">
         <f>Drivers!AO8</f>
         <v>Logano</v>
@@ -9676,11 +9718,11 @@
       </c>
       <c r="T10" s="26">
         <f>Drivers!T22</f>
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="U10" s="26">
         <f>Drivers!U22</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V10" s="26">
         <f>Drivers!V22</f>
@@ -9750,9 +9792,9 @@
         <f>Drivers!AL22</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="117"/>
-      <c r="AN10" s="124"/>
-      <c r="AO10" s="130"/>
+      <c r="AM10" s="129"/>
+      <c r="AN10" s="136"/>
+      <c r="AO10" s="142"/>
       <c r="AP10" s="2"/>
       <c r="AQ10" s="13"/>
       <c r="AR10" s="2"/>
@@ -9770,7 +9812,7 @@
       <c r="BD10" s="2"/>
     </row>
     <row r="11" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="86"/>
+      <c r="A11" s="106"/>
       <c r="B11" s="51"/>
       <c r="C11" s="44">
         <f>SUM(C9+C10)</f>
@@ -9842,11 +9884,11 @@
       </c>
       <c r="T11" s="44">
         <f t="shared" ref="T11" si="18">SUM(T9+T10)</f>
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" ref="U11" si="19">SUM(U9+U10)</f>
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="V11" s="44">
         <f t="shared" ref="V11" si="20">SUM(V9+V10)</f>
@@ -9916,9 +9958,9 @@
         <f t="shared" ref="AL11" si="36">SUM(AL9+AL10)</f>
         <v>0</v>
       </c>
-      <c r="AM11" s="119"/>
-      <c r="AN11" s="126"/>
-      <c r="AO11" s="131"/>
+      <c r="AM11" s="131"/>
+      <c r="AN11" s="138"/>
+      <c r="AO11" s="143"/>
       <c r="AP11" s="13"/>
       <c r="AQ11" s="13"/>
       <c r="AR11" s="13"/>
@@ -9936,7 +9978,7 @@
       <c r="BD11" s="13"/>
     </row>
     <row r="12" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="87" t="str">
+      <c r="A12" s="107" t="str">
         <f>Drivers!AN10</f>
         <v>Hackman</v>
       </c>
@@ -10014,11 +10056,11 @@
       </c>
       <c r="T12" s="38">
         <f>Drivers!T20</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="U12" s="38">
         <f>Drivers!U20</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V12" s="38">
         <f>Drivers!V20</f>
@@ -10088,17 +10130,17 @@
         <f>Drivers!AL20</f>
         <v>0</v>
       </c>
-      <c r="AM12" s="116">
+      <c r="AM12" s="128">
         <f>SUM(C14:AL14)</f>
-        <v>977</v>
-      </c>
-      <c r="AN12" s="127">
+        <v>1045</v>
+      </c>
+      <c r="AN12" s="139">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>3</v>
       </c>
-      <c r="AO12" s="129">
+      <c r="AO12" s="141">
         <f t="shared" ref="AO12" si="37">AVERAGE(C14:AL14)</f>
-        <v>27.138888888888889</v>
+        <v>29.027777777777779</v>
       </c>
       <c r="AP12" s="2"/>
       <c r="AQ12" s="13"/>
@@ -10117,7 +10159,7 @@
       <c r="BD12" s="2"/>
     </row>
     <row r="13" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
+      <c r="A13" s="105"/>
       <c r="B13" s="49" t="str">
         <f>Drivers!AO11</f>
         <v>Buscher</v>
@@ -10192,11 +10234,11 @@
       </c>
       <c r="T13" s="26">
         <f>Drivers!T18</f>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="U13" s="26">
         <f>Drivers!U18</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V13" s="26">
         <f>Drivers!V18</f>
@@ -10266,9 +10308,9 @@
         <f>Drivers!AL18</f>
         <v>0</v>
       </c>
-      <c r="AM13" s="117"/>
-      <c r="AN13" s="124"/>
-      <c r="AO13" s="130"/>
+      <c r="AM13" s="129"/>
+      <c r="AN13" s="136"/>
+      <c r="AO13" s="142"/>
       <c r="AP13" s="2"/>
       <c r="AQ13" s="13"/>
       <c r="AR13" s="2"/>
@@ -10286,7 +10328,7 @@
       <c r="BD13" s="2"/>
     </row>
     <row r="14" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="86"/>
+      <c r="A14" s="106"/>
       <c r="B14" s="52"/>
       <c r="C14" s="44">
         <f>SUM(C12:C13)</f>
@@ -10358,11 +10400,11 @@
       </c>
       <c r="T14" s="44">
         <f t="shared" ref="T14" si="54">SUM(T12+T13)</f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" ref="U14" si="55">SUM(U12+U13)</f>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="V14" s="44">
         <f t="shared" ref="V14" si="56">SUM(V12+V13)</f>
@@ -10432,9 +10474,9 @@
         <f t="shared" ref="AL14" si="72">SUM(AL12+AL13)</f>
         <v>0</v>
       </c>
-      <c r="AM14" s="117"/>
-      <c r="AN14" s="124"/>
-      <c r="AO14" s="131"/>
+      <c r="AM14" s="129"/>
+      <c r="AN14" s="136"/>
+      <c r="AO14" s="143"/>
       <c r="AP14" s="13"/>
       <c r="AQ14" s="13"/>
       <c r="AR14" s="13"/>
@@ -10452,7 +10494,7 @@
       <c r="BD14" s="13"/>
     </row>
     <row r="15" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="87" t="str">
+      <c r="A15" s="107" t="str">
         <f>Drivers!AN13</f>
         <v>Tony (1)</v>
       </c>
@@ -10530,11 +10572,11 @@
       </c>
       <c r="T15" s="38">
         <f>Drivers!T19</f>
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="U15" s="38">
         <f>Drivers!U19</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V15" s="38">
         <f>Drivers!V19</f>
@@ -10604,17 +10646,17 @@
         <f>Drivers!AL19</f>
         <v>0</v>
       </c>
-      <c r="AM15" s="118">
+      <c r="AM15" s="130">
         <f>SUM(C17:AL17)</f>
-        <v>883</v>
-      </c>
-      <c r="AN15" s="125">
+        <v>953</v>
+      </c>
+      <c r="AN15" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>5</v>
       </c>
-      <c r="AO15" s="129">
+      <c r="AO15" s="141">
         <f t="shared" ref="AO15" si="73">AVERAGE(C17:AL17)</f>
-        <v>24.527777777777779</v>
+        <v>26.472222222222221</v>
       </c>
       <c r="AP15" s="2"/>
       <c r="AQ15" s="13"/>
@@ -10633,7 +10675,7 @@
       <c r="BD15" s="2"/>
     </row>
     <row r="16" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A16" s="85"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="78" t="str">
         <f>Drivers!AO14</f>
         <v>Hosevar</v>
@@ -10708,11 +10750,11 @@
       </c>
       <c r="T16" s="26">
         <f>Drivers!T42</f>
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="U16" s="26">
         <f>Drivers!U42</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V16" s="26">
         <f>Drivers!V42</f>
@@ -10782,9 +10824,9 @@
         <f>Drivers!AL42</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="117"/>
-      <c r="AN16" s="124"/>
-      <c r="AO16" s="130"/>
+      <c r="AM16" s="129"/>
+      <c r="AN16" s="136"/>
+      <c r="AO16" s="142"/>
       <c r="AP16" s="2"/>
       <c r="AQ16" s="13"/>
       <c r="AR16" s="2"/>
@@ -10802,7 +10844,7 @@
       <c r="BD16" s="2"/>
     </row>
     <row r="17" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="86"/>
+      <c r="A17" s="106"/>
       <c r="B17" s="52"/>
       <c r="C17" s="44">
         <f>SUM(C15+C16)</f>
@@ -10874,11 +10916,11 @@
       </c>
       <c r="T17" s="44">
         <f t="shared" ref="T17" si="90">SUM(T15+T16)</f>
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" ref="U17" si="91">SUM(U15+U16)</f>
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="V17" s="44">
         <f t="shared" ref="V17" si="92">SUM(V15+V16)</f>
@@ -10948,9 +10990,9 @@
         <f t="shared" ref="AL17" si="108">SUM(AL15+AL16)</f>
         <v>0</v>
       </c>
-      <c r="AM17" s="119"/>
-      <c r="AN17" s="126"/>
-      <c r="AO17" s="131"/>
+      <c r="AM17" s="131"/>
+      <c r="AN17" s="138"/>
+      <c r="AO17" s="143"/>
       <c r="AP17" s="13"/>
       <c r="AQ17" s="13"/>
       <c r="AR17" s="13"/>
@@ -10968,7 +11010,7 @@
       <c r="BD17" s="13"/>
     </row>
     <row r="18" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="87" t="str">
+      <c r="A18" s="107" t="str">
         <f>Drivers!AN16</f>
         <v>Gass</v>
       </c>
@@ -11046,11 +11088,11 @@
       </c>
       <c r="T18" s="38">
         <f>Drivers!T14</f>
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="U18" s="38">
         <f>Drivers!U14</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="V18" s="38">
         <f>Drivers!V14</f>
@@ -11120,17 +11162,17 @@
         <f>Drivers!AL14</f>
         <v>0</v>
       </c>
-      <c r="AM18" s="118">
+      <c r="AM18" s="130">
         <f>SUM(C20:AL20)</f>
-        <v>1322</v>
-      </c>
-      <c r="AN18" s="127">
+        <v>1387</v>
+      </c>
+      <c r="AN18" s="139">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>1</v>
       </c>
-      <c r="AO18" s="129">
+      <c r="AO18" s="141">
         <f t="shared" ref="AO18" si="109">AVERAGE(C20:AL20)</f>
-        <v>36.722222222222221</v>
+        <v>38.527777777777779</v>
       </c>
       <c r="AP18" s="2"/>
       <c r="AQ18" s="13"/>
@@ -11149,7 +11191,7 @@
       <c r="BD18" s="2"/>
     </row>
     <row r="19" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A19" s="85"/>
+      <c r="A19" s="105"/>
       <c r="B19" s="49" t="str">
         <f>Drivers!AO17</f>
         <v>Gibbs</v>
@@ -11224,11 +11266,11 @@
       </c>
       <c r="T19" s="26">
         <f>Drivers!T39</f>
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="U19" s="26">
         <f>Drivers!U39</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="V19" s="26">
         <f>Drivers!V39</f>
@@ -11298,9 +11340,9 @@
         <f>Drivers!AL39</f>
         <v>0</v>
       </c>
-      <c r="AM19" s="117"/>
-      <c r="AN19" s="124"/>
-      <c r="AO19" s="130"/>
+      <c r="AM19" s="129"/>
+      <c r="AN19" s="136"/>
+      <c r="AO19" s="142"/>
       <c r="AP19" s="2"/>
       <c r="AQ19" s="13"/>
       <c r="AR19" s="2"/>
@@ -11318,7 +11360,7 @@
       <c r="BD19" s="2"/>
     </row>
     <row r="20" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="86"/>
+      <c r="A20" s="106"/>
       <c r="B20" s="52"/>
       <c r="C20" s="44">
         <f>SUM(C18+C19)</f>
@@ -11390,11 +11432,11 @@
       </c>
       <c r="T20" s="44">
         <f t="shared" ref="T20" si="126">SUM(T18+T19)</f>
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" ref="U20" si="127">SUM(U18+U19)</f>
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="V20" s="44">
         <f t="shared" ref="V20" si="128">SUM(V18+V19)</f>
@@ -11464,9 +11506,9 @@
         <f t="shared" ref="AL20" si="144">SUM(AL18+AL19)</f>
         <v>0</v>
       </c>
-      <c r="AM20" s="119"/>
-      <c r="AN20" s="124"/>
-      <c r="AO20" s="131"/>
+      <c r="AM20" s="131"/>
+      <c r="AN20" s="136"/>
+      <c r="AO20" s="143"/>
       <c r="AP20" s="13"/>
       <c r="AQ20" s="13"/>
       <c r="AR20" s="13"/>
@@ -11484,7 +11526,7 @@
       <c r="BD20" s="13"/>
     </row>
     <row r="21" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87" t="str">
+      <c r="A21" s="107" t="str">
         <f>Drivers!AN19</f>
         <v>Kilhefner (3)</v>
       </c>
@@ -11562,11 +11604,11 @@
       </c>
       <c r="T21" s="38">
         <f>Drivers!T15</f>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="U21" s="38">
         <f>Drivers!U15</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V21" s="38">
         <f>Drivers!V15</f>
@@ -11636,17 +11678,17 @@
         <f>Drivers!AL15</f>
         <v>0</v>
       </c>
-      <c r="AM21" s="118">
+      <c r="AM21" s="130">
         <f>SUM(C23:AL23)</f>
-        <v>863</v>
-      </c>
-      <c r="AN21" s="125">
+        <v>924</v>
+      </c>
+      <c r="AN21" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>6</v>
       </c>
-      <c r="AO21" s="129">
+      <c r="AO21" s="141">
         <f t="shared" ref="AO21" si="145">AVERAGE(C23:AL23)</f>
-        <v>23.972222222222221</v>
+        <v>25.666666666666668</v>
       </c>
       <c r="AP21" s="2"/>
       <c r="AQ21" s="13"/>
@@ -11665,7 +11707,7 @@
       <c r="BD21" s="2"/>
     </row>
     <row r="22" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A22" s="85"/>
+      <c r="A22" s="105"/>
       <c r="B22" s="78" t="str">
         <f>Drivers!AO20</f>
         <v>Chastain</v>
@@ -11740,11 +11782,11 @@
       </c>
       <c r="T22" s="26">
         <f>Drivers!T4</f>
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="U22" s="26">
         <f>Drivers!U4</f>
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="V22" s="26">
         <f>Drivers!V4</f>
@@ -11814,9 +11856,9 @@
         <f>Drivers!AL4</f>
         <v>0</v>
       </c>
-      <c r="AM22" s="117"/>
-      <c r="AN22" s="124"/>
-      <c r="AO22" s="130"/>
+      <c r="AM22" s="129"/>
+      <c r="AN22" s="136"/>
+      <c r="AO22" s="142"/>
       <c r="AP22" s="2"/>
       <c r="AQ22" s="13"/>
       <c r="AR22" s="2"/>
@@ -11834,7 +11876,7 @@
       <c r="BD22" s="2"/>
     </row>
     <row r="23" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="86"/>
+      <c r="A23" s="106"/>
       <c r="B23" s="51"/>
       <c r="C23" s="44">
         <f>SUM(C21+C22)</f>
@@ -11906,11 +11948,11 @@
       </c>
       <c r="T23" s="44">
         <f t="shared" ref="T23" si="162">SUM(T21+T22)</f>
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" ref="U23" si="163">SUM(U21+U22)</f>
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="V23" s="44">
         <f t="shared" ref="V23" si="164">SUM(V21+V22)</f>
@@ -11980,9 +12022,9 @@
         <f t="shared" ref="AL23" si="180">SUM(AL21+AL22)</f>
         <v>0</v>
       </c>
-      <c r="AM23" s="119"/>
-      <c r="AN23" s="126"/>
-      <c r="AO23" s="131"/>
+      <c r="AM23" s="131"/>
+      <c r="AN23" s="138"/>
+      <c r="AO23" s="143"/>
       <c r="AP23" s="13"/>
       <c r="AQ23" s="13"/>
       <c r="AR23" s="13"/>
@@ -12000,7 +12042,7 @@
       <c r="BD23" s="13"/>
     </row>
     <row r="24" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87" t="str">
+      <c r="A24" s="107" t="str">
         <f>Drivers!AN22</f>
         <v>Dani(1)</v>
       </c>
@@ -12078,11 +12120,11 @@
       </c>
       <c r="T24" s="38">
         <f>Drivers!T8</f>
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="U24" s="38">
         <f>Drivers!U8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V24" s="38">
         <f>Drivers!V8</f>
@@ -12152,17 +12194,17 @@
         <f>Drivers!AL8</f>
         <v>0</v>
       </c>
-      <c r="AM24" s="116">
+      <c r="AM24" s="128">
         <f>SUM(C26:AL26)</f>
-        <v>913</v>
-      </c>
-      <c r="AN24" s="127">
+        <v>963</v>
+      </c>
+      <c r="AN24" s="139">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>4</v>
       </c>
-      <c r="AO24" s="129">
+      <c r="AO24" s="141">
         <f t="shared" ref="AO24" si="181">AVERAGE(C26:AL26)</f>
-        <v>25.361111111111111</v>
+        <v>26.75</v>
       </c>
       <c r="AP24" s="2"/>
       <c r="AQ24" s="13"/>
@@ -12181,7 +12223,7 @@
       <c r="BD24" s="2"/>
     </row>
     <row r="25" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="78" t="str">
         <f>Drivers!AO23</f>
         <v>Bubba</v>
@@ -12256,11 +12298,11 @@
       </c>
       <c r="T25" s="26">
         <f>Drivers!T23</f>
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="U25" s="26">
         <f>Drivers!U23</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V25" s="26">
         <f>Drivers!V23</f>
@@ -12330,9 +12372,9 @@
         <f>Drivers!AL23</f>
         <v>0</v>
       </c>
-      <c r="AM25" s="117"/>
-      <c r="AN25" s="124"/>
-      <c r="AO25" s="130"/>
+      <c r="AM25" s="129"/>
+      <c r="AN25" s="136"/>
+      <c r="AO25" s="142"/>
       <c r="AP25" s="2"/>
       <c r="AQ25" s="13"/>
       <c r="AR25" s="2"/>
@@ -12350,7 +12392,7 @@
       <c r="BD25" s="2"/>
     </row>
     <row r="26" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="86"/>
+      <c r="A26" s="106"/>
       <c r="B26" s="52"/>
       <c r="C26" s="44">
         <f>SUM(C24+C25)</f>
@@ -12422,11 +12464,11 @@
       </c>
       <c r="T26" s="44">
         <f t="shared" ref="T26" si="198">SUM(T24+T25)</f>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" ref="U26" si="199">SUM(U24+U25)</f>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="V26" s="44">
         <f t="shared" ref="V26" si="200">SUM(V24+V25)</f>
@@ -12496,9 +12538,9 @@
         <f t="shared" ref="AL26" si="216">SUM(AL24+AL25)</f>
         <v>0</v>
       </c>
-      <c r="AM26" s="117"/>
-      <c r="AN26" s="124"/>
-      <c r="AO26" s="131"/>
+      <c r="AM26" s="129"/>
+      <c r="AN26" s="136"/>
+      <c r="AO26" s="143"/>
       <c r="AP26" s="13"/>
       <c r="AQ26" s="13"/>
       <c r="AR26" s="13"/>
@@ -12516,7 +12558,7 @@
       <c r="BD26" s="13"/>
     </row>
     <row r="27" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87">
+      <c r="A27" s="107">
         <f>Drivers!AN25</f>
         <v>8</v>
       </c>
@@ -12560,15 +12602,15 @@
       <c r="AJ27" s="58"/>
       <c r="AK27" s="58"/>
       <c r="AL27" s="43"/>
-      <c r="AM27" s="118">
+      <c r="AM27" s="130">
         <f>SUM(C29:AL29)</f>
         <v>0</v>
       </c>
-      <c r="AN27" s="125">
+      <c r="AN27" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>8</v>
       </c>
-      <c r="AO27" s="129">
+      <c r="AO27" s="141">
         <f t="shared" ref="AO27" si="217">AVERAGE(C29:AL29)</f>
         <v>0</v>
       </c>
@@ -12589,7 +12631,7 @@
       <c r="BD27" s="2"/>
     </row>
     <row r="28" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A28" s="85"/>
+      <c r="A28" s="105"/>
       <c r="B28" s="49" t="str">
         <f>Drivers!AO26</f>
         <v>B</v>
@@ -12630,9 +12672,9 @@
       <c r="AJ28" s="55"/>
       <c r="AK28" s="55"/>
       <c r="AL28" s="30"/>
-      <c r="AM28" s="117"/>
-      <c r="AN28" s="124"/>
-      <c r="AO28" s="130"/>
+      <c r="AM28" s="129"/>
+      <c r="AN28" s="136"/>
+      <c r="AO28" s="142"/>
       <c r="AP28" s="2"/>
       <c r="AQ28" s="13"/>
       <c r="AR28" s="2"/>
@@ -12650,7 +12692,7 @@
       <c r="BD28" s="2"/>
     </row>
     <row r="29" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="86"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="52"/>
       <c r="C29" s="44">
         <f>SUM(C27+C28)</f>
@@ -12796,9 +12838,9 @@
         <f t="shared" ref="AL29" si="252">SUM(AL27+AL28)</f>
         <v>0</v>
       </c>
-      <c r="AM29" s="117"/>
-      <c r="AN29" s="126"/>
-      <c r="AO29" s="131"/>
+      <c r="AM29" s="129"/>
+      <c r="AN29" s="138"/>
+      <c r="AO29" s="143"/>
       <c r="AP29" s="13"/>
       <c r="AQ29" s="13"/>
       <c r="AR29" s="13"/>
@@ -12816,7 +12858,7 @@
       <c r="BD29" s="13"/>
     </row>
     <row r="30" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="103">
+      <c r="A30" s="119">
         <f>Drivers!AN28</f>
         <v>9</v>
       </c>
@@ -12860,15 +12902,15 @@
       <c r="AJ30" s="40"/>
       <c r="AK30" s="40"/>
       <c r="AL30" s="43"/>
-      <c r="AM30" s="118">
+      <c r="AM30" s="130">
         <f>SUM(C32:AL32)</f>
         <v>0</v>
       </c>
-      <c r="AN30" s="125">
+      <c r="AN30" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>8</v>
       </c>
-      <c r="AO30" s="129">
+      <c r="AO30" s="141">
         <f t="shared" ref="AO30" si="253">AVERAGE(C32:AL32)</f>
         <v>0</v>
       </c>
@@ -12889,7 +12931,7 @@
       <c r="BD30" s="2"/>
     </row>
     <row r="31" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A31" s="85"/>
+      <c r="A31" s="105"/>
       <c r="B31" s="49" t="str">
         <f>Drivers!AO29</f>
         <v>B</v>
@@ -12930,9 +12972,9 @@
       <c r="AJ31" s="33"/>
       <c r="AK31" s="33"/>
       <c r="AL31" s="30"/>
-      <c r="AM31" s="117"/>
-      <c r="AN31" s="124"/>
-      <c r="AO31" s="130"/>
+      <c r="AM31" s="129"/>
+      <c r="AN31" s="136"/>
+      <c r="AO31" s="142"/>
       <c r="AP31" s="2"/>
       <c r="AQ31" s="13"/>
       <c r="AR31" s="2"/>
@@ -12950,7 +12992,7 @@
       <c r="BD31" s="2"/>
     </row>
     <row r="32" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A32" s="85"/>
+      <c r="A32" s="105"/>
       <c r="B32" s="52"/>
       <c r="C32" s="44">
         <f>SUM(C30+C31)</f>
@@ -13096,9 +13138,9 @@
         <f t="shared" ref="AL32" si="288">SUM(AL30+AL31)</f>
         <v>0</v>
       </c>
-      <c r="AM32" s="119"/>
-      <c r="AN32" s="126"/>
-      <c r="AO32" s="131"/>
+      <c r="AM32" s="131"/>
+      <c r="AN32" s="138"/>
+      <c r="AO32" s="143"/>
       <c r="AP32" s="13"/>
       <c r="AQ32" s="13"/>
       <c r="AR32" s="13"/>
@@ -13116,7 +13158,7 @@
       <c r="BD32" s="13"/>
     </row>
     <row r="33" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="87">
+      <c r="A33" s="107">
         <f>Drivers!AN31</f>
         <v>10</v>
       </c>
@@ -13160,15 +13202,15 @@
       <c r="AJ33" s="33"/>
       <c r="AK33" s="33"/>
       <c r="AL33" s="30"/>
-      <c r="AM33" s="116">
+      <c r="AM33" s="128">
         <f>SUM(C35:AL35)</f>
         <v>0</v>
       </c>
-      <c r="AN33" s="125">
+      <c r="AN33" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>8</v>
       </c>
-      <c r="AO33" s="132"/>
+      <c r="AO33" s="144"/>
       <c r="AP33" s="2"/>
       <c r="AQ33" s="13"/>
       <c r="AR33" s="2"/>
@@ -13186,7 +13228,7 @@
       <c r="BD33" s="2"/>
     </row>
     <row r="34" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A34" s="85"/>
+      <c r="A34" s="105"/>
       <c r="B34" s="49" t="str">
         <f>Drivers!AO32</f>
         <v>B</v>
@@ -13227,9 +13269,9 @@
       <c r="AJ34" s="33"/>
       <c r="AK34" s="33"/>
       <c r="AL34" s="30"/>
-      <c r="AM34" s="117"/>
-      <c r="AN34" s="124"/>
-      <c r="AO34" s="124"/>
+      <c r="AM34" s="129"/>
+      <c r="AN34" s="136"/>
+      <c r="AO34" s="136"/>
       <c r="AP34" s="2"/>
       <c r="AQ34" s="13"/>
       <c r="AR34" s="2"/>
@@ -13247,7 +13289,7 @@
       <c r="BD34" s="2"/>
     </row>
     <row r="35" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="86"/>
+      <c r="A35" s="106"/>
       <c r="B35" s="54"/>
       <c r="C35" s="35">
         <f>SUM(C33+C34)</f>
@@ -13393,9 +13435,9 @@
         <f t="shared" ref="AL35" si="323">SUM(AL33+AL34)</f>
         <v>0</v>
       </c>
-      <c r="AM35" s="122"/>
-      <c r="AN35" s="128"/>
-      <c r="AO35" s="128"/>
+      <c r="AM35" s="134"/>
+      <c r="AN35" s="140"/>
+      <c r="AO35" s="140"/>
       <c r="AP35" s="13"/>
       <c r="AQ35" s="13"/>
       <c r="AR35" s="13"/>
@@ -18196,28 +18238,28 @@
     </row>
     <row r="121" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A121" s="21"/>
-      <c r="C121" s="120"/>
-      <c r="D121" s="121"/>
-      <c r="E121" s="121"/>
-      <c r="F121" s="121"/>
-      <c r="G121" s="121"/>
-      <c r="H121" s="121"/>
-      <c r="I121" s="121"/>
-      <c r="J121" s="121"/>
-      <c r="K121" s="121"/>
-      <c r="L121" s="121"/>
+      <c r="C121" s="132"/>
+      <c r="D121" s="133"/>
+      <c r="E121" s="133"/>
+      <c r="F121" s="133"/>
+      <c r="G121" s="133"/>
+      <c r="H121" s="133"/>
+      <c r="I121" s="133"/>
+      <c r="J121" s="133"/>
+      <c r="K121" s="133"/>
+      <c r="L121" s="133"/>
     </row>
     <row r="122" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="C122" s="121"/>
-      <c r="D122" s="121"/>
-      <c r="E122" s="121"/>
-      <c r="F122" s="121"/>
-      <c r="G122" s="121"/>
-      <c r="H122" s="121"/>
-      <c r="I122" s="121"/>
-      <c r="J122" s="121"/>
-      <c r="K122" s="121"/>
-      <c r="L122" s="121"/>
+      <c r="C122" s="133"/>
+      <c r="D122" s="133"/>
+      <c r="E122" s="133"/>
+      <c r="F122" s="133"/>
+      <c r="G122" s="133"/>
+      <c r="H122" s="133"/>
+      <c r="I122" s="133"/>
+      <c r="J122" s="133"/>
+      <c r="K122" s="133"/>
+      <c r="L122" s="133"/>
     </row>
     <row r="123" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A123" s="21"/>
@@ -18470,355 +18512,355 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:56" ht="22" x14ac:dyDescent="0.25">
-      <c r="A1" s="81">
+      <c r="A1" s="101">
         <v>2025</v>
       </c>
-      <c r="B1" s="82"/>
+      <c r="B1" s="102"/>
       <c r="C1" s="145" t="s">
         <v>74</v>
       </c>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="J1" s="82"/>
-      <c r="K1" s="82"/>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="T1" s="82"/>
-      <c r="U1" s="82"/>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="82"/>
-      <c r="Y1" s="82"/>
-      <c r="Z1" s="82"/>
-      <c r="AA1" s="82"/>
-      <c r="AB1" s="82"/>
-      <c r="AC1" s="82"/>
-      <c r="AD1" s="82"/>
-      <c r="AE1" s="82"/>
-      <c r="AF1" s="82"/>
-      <c r="AG1" s="82"/>
-      <c r="AH1" s="82"/>
-      <c r="AI1" s="82"/>
-      <c r="AJ1" s="82"/>
-      <c r="AK1" s="82"/>
-      <c r="AL1" s="82"/>
-      <c r="AM1" s="82"/>
-      <c r="AN1" s="82"/>
-      <c r="AO1" s="82"/>
+      <c r="D1" s="102"/>
+      <c r="E1" s="102"/>
+      <c r="F1" s="102"/>
+      <c r="G1" s="102"/>
+      <c r="H1" s="102"/>
+      <c r="I1" s="102"/>
+      <c r="J1" s="102"/>
+      <c r="K1" s="102"/>
+      <c r="L1" s="102"/>
+      <c r="M1" s="102"/>
+      <c r="N1" s="102"/>
+      <c r="O1" s="102"/>
+      <c r="P1" s="102"/>
+      <c r="Q1" s="102"/>
+      <c r="R1" s="102"/>
+      <c r="S1" s="102"/>
+      <c r="T1" s="102"/>
+      <c r="U1" s="102"/>
+      <c r="V1" s="102"/>
+      <c r="W1" s="102"/>
+      <c r="X1" s="102"/>
+      <c r="Y1" s="102"/>
+      <c r="Z1" s="102"/>
+      <c r="AA1" s="102"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="102"/>
+      <c r="AD1" s="102"/>
+      <c r="AE1" s="102"/>
+      <c r="AF1" s="102"/>
+      <c r="AG1" s="102"/>
+      <c r="AH1" s="102"/>
+      <c r="AI1" s="102"/>
+      <c r="AJ1" s="102"/>
+      <c r="AK1" s="102"/>
+      <c r="AL1" s="102"/>
+      <c r="AM1" s="102"/>
+      <c r="AN1" s="102"/>
+      <c r="AO1" s="102"/>
       <c r="AP1" s="48"/>
     </row>
     <row r="2" spans="1:56" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="83"/>
-      <c r="X2" s="83"/>
-      <c r="Y2" s="83"/>
-      <c r="Z2" s="83"/>
-      <c r="AA2" s="83"/>
-      <c r="AB2" s="83"/>
-      <c r="AC2" s="83"/>
-      <c r="AD2" s="83"/>
-      <c r="AE2" s="83"/>
-      <c r="AF2" s="83"/>
-      <c r="AG2" s="83"/>
-      <c r="AH2" s="83"/>
-      <c r="AI2" s="83"/>
-      <c r="AJ2" s="83"/>
-      <c r="AK2" s="83"/>
-      <c r="AL2" s="83"/>
-      <c r="AM2" s="83"/>
-      <c r="AN2" s="83"/>
-      <c r="AO2" s="83"/>
+      <c r="A2" s="103"/>
+      <c r="B2" s="103"/>
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+      <c r="H2" s="103"/>
+      <c r="I2" s="103"/>
+      <c r="J2" s="103"/>
+      <c r="K2" s="103"/>
+      <c r="L2" s="103"/>
+      <c r="M2" s="103"/>
+      <c r="N2" s="103"/>
+      <c r="O2" s="103"/>
+      <c r="P2" s="103"/>
+      <c r="Q2" s="103"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="103"/>
+      <c r="T2" s="103"/>
+      <c r="U2" s="103"/>
+      <c r="V2" s="103"/>
+      <c r="W2" s="103"/>
+      <c r="X2" s="103"/>
+      <c r="Y2" s="103"/>
+      <c r="Z2" s="103"/>
+      <c r="AA2" s="103"/>
+      <c r="AB2" s="103"/>
+      <c r="AC2" s="103"/>
+      <c r="AD2" s="103"/>
+      <c r="AE2" s="103"/>
+      <c r="AF2" s="103"/>
+      <c r="AG2" s="103"/>
+      <c r="AH2" s="103"/>
+      <c r="AI2" s="103"/>
+      <c r="AJ2" s="103"/>
+      <c r="AK2" s="103"/>
+      <c r="AL2" s="103"/>
+      <c r="AM2" s="103"/>
+      <c r="AN2" s="103"/>
+      <c r="AO2" s="103"/>
       <c r="AP2" s="48"/>
     </row>
     <row r="3" spans="1:56" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="D3" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="97" t="s">
+      <c r="E3" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="100" t="s">
+      <c r="F3" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="100" t="s">
+      <c r="H3" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="97" t="s">
+      <c r="I3" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="100" t="s">
+      <c r="J3" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="97" t="s">
+      <c r="K3" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="97" t="s">
+      <c r="L3" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="97" t="s">
+      <c r="N3" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="97" t="s">
+      <c r="O3" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="97" t="s">
+      <c r="P3" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="97" t="s">
+      <c r="Q3" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="97" t="s">
+      <c r="R3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="97" t="s">
+      <c r="S3" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="97" t="s">
+      <c r="T3" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="97" t="s">
+      <c r="U3" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="97" t="s">
+      <c r="V3" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="97" t="s">
+      <c r="W3" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="X3" s="97" t="s">
+      <c r="X3" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="Y3" s="97" t="s">
+      <c r="Y3" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="Z3" s="97" t="s">
+      <c r="Z3" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="AA3" s="97" t="s">
+      <c r="AA3" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="AB3" s="97" t="s">
+      <c r="AB3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="AC3" s="100" t="s">
+      <c r="AC3" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="AD3" s="97" t="s">
+      <c r="AD3" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="97" t="s">
+      <c r="AE3" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="AF3" s="97" t="s">
+      <c r="AF3" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="AG3" s="97" t="s">
+      <c r="AG3" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="AH3" s="97" t="s">
+      <c r="AH3" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="AI3" s="97" t="s">
+      <c r="AI3" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="AJ3" s="97" t="s">
+      <c r="AJ3" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="AK3" s="97" t="s">
+      <c r="AK3" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="AL3" s="107" t="s">
+      <c r="AL3" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="AM3" s="88" t="s">
+      <c r="AM3" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="AN3" s="91" t="s">
+      <c r="AN3" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="AO3" s="94" t="s">
+      <c r="AO3" s="114" t="s">
         <v>41</v>
       </c>
       <c r="AP3" s="47"/>
-      <c r="AQ3" s="104"/>
-      <c r="AR3" s="104"/>
-      <c r="AS3" s="104"/>
-      <c r="AT3" s="104"/>
-      <c r="AU3" s="104"/>
-      <c r="AV3" s="104"/>
-      <c r="AW3" s="104"/>
-      <c r="AX3" s="104"/>
-      <c r="AY3" s="104"/>
-      <c r="AZ3" s="104"/>
-      <c r="BA3" s="104"/>
-      <c r="BB3" s="104"/>
-      <c r="BC3" s="104"/>
-      <c r="BD3" s="104"/>
+      <c r="AQ3" s="120"/>
+      <c r="AR3" s="120"/>
+      <c r="AS3" s="120"/>
+      <c r="AT3" s="120"/>
+      <c r="AU3" s="120"/>
+      <c r="AV3" s="120"/>
+      <c r="AW3" s="120"/>
+      <c r="AX3" s="120"/>
+      <c r="AY3" s="120"/>
+      <c r="AZ3" s="120"/>
+      <c r="BA3" s="120"/>
+      <c r="BB3" s="120"/>
+      <c r="BC3" s="120"/>
+      <c r="BD3" s="120"/>
     </row>
     <row r="4" spans="1:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="114"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98"/>
-      <c r="W4" s="98"/>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="98"/>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="98"/>
-      <c r="AK4" s="98"/>
-      <c r="AL4" s="108"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="92"/>
-      <c r="AO4" s="95"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="W4" s="88"/>
+      <c r="X4" s="88"/>
+      <c r="Y4" s="88"/>
+      <c r="Z4" s="88"/>
+      <c r="AA4" s="88"/>
+      <c r="AB4" s="88"/>
+      <c r="AC4" s="85"/>
+      <c r="AD4" s="88"/>
+      <c r="AE4" s="88"/>
+      <c r="AF4" s="88"/>
+      <c r="AG4" s="88"/>
+      <c r="AH4" s="88"/>
+      <c r="AI4" s="88"/>
+      <c r="AJ4" s="88"/>
+      <c r="AK4" s="88"/>
+      <c r="AL4" s="92"/>
+      <c r="AM4" s="109"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="115"/>
       <c r="AP4" s="47"/>
-      <c r="AQ4" s="106"/>
-      <c r="AR4" s="105"/>
-      <c r="AS4" s="106"/>
-      <c r="AT4" s="105"/>
-      <c r="AU4" s="106"/>
-      <c r="AV4" s="105"/>
-      <c r="AW4" s="106"/>
-      <c r="AX4" s="105"/>
-      <c r="AY4" s="106"/>
-      <c r="AZ4" s="105"/>
-      <c r="BA4" s="106"/>
-      <c r="BB4" s="105"/>
-      <c r="BC4" s="106"/>
-      <c r="BD4" s="105"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="121"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="121"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="121"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="121"/>
+      <c r="BA4" s="122"/>
+      <c r="BB4" s="121"/>
+      <c r="BC4" s="122"/>
+      <c r="BD4" s="121"/>
     </row>
     <row r="5" spans="1:56" ht="11" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="115"/>
-      <c r="B5" s="112"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="99"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="99"/>
-      <c r="V5" s="99"/>
-      <c r="W5" s="99"/>
-      <c r="X5" s="99"/>
-      <c r="Y5" s="99"/>
-      <c r="Z5" s="99"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="99"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="99"/>
-      <c r="AF5" s="99"/>
-      <c r="AG5" s="99"/>
-      <c r="AH5" s="99"/>
-      <c r="AI5" s="99"/>
-      <c r="AJ5" s="99"/>
-      <c r="AK5" s="99"/>
-      <c r="AL5" s="109"/>
-      <c r="AM5" s="90"/>
-      <c r="AN5" s="93"/>
-      <c r="AO5" s="96"/>
+      <c r="A5" s="127"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="117"/>
+      <c r="W5" s="117"/>
+      <c r="X5" s="117"/>
+      <c r="Y5" s="117"/>
+      <c r="Z5" s="117"/>
+      <c r="AA5" s="117"/>
+      <c r="AB5" s="117"/>
+      <c r="AC5" s="118"/>
+      <c r="AD5" s="117"/>
+      <c r="AE5" s="117"/>
+      <c r="AF5" s="117"/>
+      <c r="AG5" s="117"/>
+      <c r="AH5" s="117"/>
+      <c r="AI5" s="117"/>
+      <c r="AJ5" s="117"/>
+      <c r="AK5" s="117"/>
+      <c r="AL5" s="123"/>
+      <c r="AM5" s="110"/>
+      <c r="AN5" s="113"/>
+      <c r="AO5" s="116"/>
       <c r="AP5" s="47"/>
-      <c r="AQ5" s="106"/>
-      <c r="AR5" s="105"/>
-      <c r="AS5" s="106"/>
-      <c r="AT5" s="105"/>
-      <c r="AU5" s="106"/>
-      <c r="AV5" s="105"/>
-      <c r="AW5" s="106"/>
-      <c r="AX5" s="105"/>
-      <c r="AY5" s="106"/>
-      <c r="AZ5" s="105"/>
-      <c r="BA5" s="106"/>
-      <c r="BB5" s="105"/>
-      <c r="BC5" s="106"/>
-      <c r="BD5" s="105"/>
+      <c r="AQ5" s="122"/>
+      <c r="AR5" s="121"/>
+      <c r="AS5" s="122"/>
+      <c r="AT5" s="121"/>
+      <c r="AU5" s="122"/>
+      <c r="AV5" s="121"/>
+      <c r="AW5" s="122"/>
+      <c r="AX5" s="121"/>
+      <c r="AY5" s="122"/>
+      <c r="AZ5" s="121"/>
+      <c r="BA5" s="122"/>
+      <c r="BB5" s="121"/>
+      <c r="BC5" s="122"/>
+      <c r="BD5" s="121"/>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="str">
+      <c r="A6" s="104" t="str">
         <f>Drivers!AQ4</f>
         <v>Dustin</v>
       </c>
@@ -18896,11 +18938,11 @@
       </c>
       <c r="T6" s="25">
         <f>Drivers!T19</f>
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="U6" s="25">
         <f>Drivers!U19</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V6" s="25">
         <f>Drivers!V19</f>
@@ -18970,21 +19012,21 @@
         <f>Drivers!AL19</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="116">
+      <c r="AM6" s="128">
         <f>SUM(C8:AL8)</f>
-        <v>872</v>
-      </c>
-      <c r="AN6" s="123">
+        <v>922</v>
+      </c>
+      <c r="AN6" s="135">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>7</v>
       </c>
-      <c r="AO6" s="129">
+      <c r="AO6" s="141">
         <f>AVERAGE(C8:AL8)</f>
-        <v>24.222222222222221</v>
+        <v>25.611111111111111</v>
       </c>
     </row>
     <row r="7" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="85"/>
+      <c r="A7" s="105"/>
       <c r="B7" s="49" t="str">
         <f>Drivers!AR5</f>
         <v>Logano</v>
@@ -19059,11 +19101,11 @@
       </c>
       <c r="T7" s="26">
         <f>Drivers!T22</f>
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="U7" s="26">
         <f>Drivers!U22</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V7" s="26">
         <f>Drivers!V22</f>
@@ -19133,9 +19175,9 @@
         <f>Drivers!AL22</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="117"/>
-      <c r="AN7" s="124"/>
-      <c r="AO7" s="130"/>
+      <c r="AM7" s="129"/>
+      <c r="AN7" s="136"/>
+      <c r="AO7" s="142"/>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2"/>
       <c r="AR7" s="2"/>
@@ -19153,7 +19195,7 @@
       <c r="BD7" s="2"/>
     </row>
     <row r="8" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="86"/>
+      <c r="A8" s="106"/>
       <c r="B8" s="49"/>
       <c r="C8" s="27">
         <f>SUM(C6+C7)</f>
@@ -19225,11 +19267,11 @@
       </c>
       <c r="T8" s="27">
         <f t="shared" si="0"/>
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="U8" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="V8" s="27">
         <f t="shared" si="0"/>
@@ -19299,9 +19341,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM8" s="117"/>
-      <c r="AN8" s="124"/>
-      <c r="AO8" s="131"/>
+      <c r="AM8" s="129"/>
+      <c r="AN8" s="136"/>
+      <c r="AO8" s="143"/>
       <c r="AP8" s="13"/>
       <c r="AQ8" s="13"/>
       <c r="AR8" s="13"/>
@@ -19319,7 +19361,7 @@
       <c r="BD8" s="13"/>
     </row>
     <row r="9" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="87" t="str">
+      <c r="A9" s="107" t="str">
         <f>Drivers!AQ7</f>
         <v>Derrick</v>
       </c>
@@ -19397,11 +19439,11 @@
       </c>
       <c r="T9" s="38">
         <f>Drivers!T20</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="U9" s="38">
         <f>Drivers!U20</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V9" s="38">
         <f>Drivers!V20</f>
@@ -19471,17 +19513,17 @@
         <f>Drivers!AL20</f>
         <v>0</v>
       </c>
-      <c r="AM9" s="118">
+      <c r="AM9" s="130">
         <f>SUM(C11:AL11)</f>
-        <v>977</v>
-      </c>
-      <c r="AN9" s="125">
+        <v>1045</v>
+      </c>
+      <c r="AN9" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
-        <v>5</v>
-      </c>
-      <c r="AO9" s="129">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="141">
         <f t="shared" ref="AO9" si="1">AVERAGE(C11:AL11)</f>
-        <v>27.138888888888889</v>
+        <v>29.027777777777779</v>
       </c>
       <c r="AP9" s="2"/>
       <c r="AQ9" s="13"/>
@@ -19500,7 +19542,7 @@
       <c r="BD9" s="2"/>
     </row>
     <row r="10" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="85"/>
+      <c r="A10" s="105"/>
       <c r="B10" s="49" t="str">
         <f>Drivers!AR8</f>
         <v>Buscher</v>
@@ -19575,11 +19617,11 @@
       </c>
       <c r="T10" s="26">
         <f>Drivers!T18</f>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="U10" s="26">
         <f>Drivers!U18</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V10" s="26">
         <f>Drivers!V18</f>
@@ -19649,9 +19691,9 @@
         <f>Drivers!AL18</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="117"/>
-      <c r="AN10" s="124"/>
-      <c r="AO10" s="130"/>
+      <c r="AM10" s="129"/>
+      <c r="AN10" s="136"/>
+      <c r="AO10" s="142"/>
       <c r="AP10" s="2"/>
       <c r="AQ10" s="13"/>
       <c r="AR10" s="2"/>
@@ -19669,7 +19711,7 @@
       <c r="BD10" s="2"/>
     </row>
     <row r="11" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="86"/>
+      <c r="A11" s="106"/>
       <c r="B11" s="51"/>
       <c r="C11" s="44">
         <f>SUM(C9+C10)</f>
@@ -19741,11 +19783,11 @@
       </c>
       <c r="T11" s="44">
         <f t="shared" si="2"/>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="V11" s="44">
         <f t="shared" si="2"/>
@@ -19815,9 +19857,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AM11" s="119"/>
-      <c r="AN11" s="126"/>
-      <c r="AO11" s="131"/>
+      <c r="AM11" s="131"/>
+      <c r="AN11" s="138"/>
+      <c r="AO11" s="143"/>
       <c r="AP11" s="13"/>
       <c r="AQ11" s="13"/>
       <c r="AR11" s="13"/>
@@ -19835,7 +19877,7 @@
       <c r="BD11" s="13"/>
     </row>
     <row r="12" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="87" t="str">
+      <c r="A12" s="107" t="str">
         <f>Drivers!AQ10</f>
         <v>Kevin</v>
       </c>
@@ -19913,11 +19955,11 @@
       </c>
       <c r="T12" s="38">
         <f>Drivers!T8</f>
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="U12" s="38">
         <f>Drivers!U8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V12" s="38">
         <f>Drivers!V8</f>
@@ -19987,17 +20029,17 @@
         <f>Drivers!AL8</f>
         <v>0</v>
       </c>
-      <c r="AM12" s="116">
+      <c r="AM12" s="128">
         <f>SUM(C14:AL14)</f>
-        <v>991</v>
-      </c>
-      <c r="AN12" s="127">
+        <v>1041</v>
+      </c>
+      <c r="AN12" s="139">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
-        <v>4</v>
-      </c>
-      <c r="AO12" s="129">
+        <v>5</v>
+      </c>
+      <c r="AO12" s="141">
         <f t="shared" ref="AO12" si="3">AVERAGE(C14:AL14)</f>
-        <v>27.527777777777779</v>
+        <v>28.916666666666668</v>
       </c>
       <c r="AP12" s="2"/>
       <c r="AQ12" s="13"/>
@@ -20016,7 +20058,7 @@
       <c r="BD12" s="2"/>
     </row>
     <row r="13" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
+      <c r="A13" s="105"/>
       <c r="B13" s="49" t="str">
         <f>Drivers!AR11</f>
         <v>Wallace</v>
@@ -20091,11 +20133,11 @@
       </c>
       <c r="T13" s="26">
         <f>Drivers!T23</f>
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="U13" s="26">
         <f>Drivers!U23</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V13" s="26">
         <f>Drivers!V23</f>
@@ -20165,9 +20207,9 @@
         <f>Drivers!AL23</f>
         <v>0</v>
       </c>
-      <c r="AM13" s="117"/>
-      <c r="AN13" s="124"/>
-      <c r="AO13" s="130"/>
+      <c r="AM13" s="129"/>
+      <c r="AN13" s="136"/>
+      <c r="AO13" s="142"/>
       <c r="AP13" s="2"/>
       <c r="AQ13" s="13"/>
       <c r="AR13" s="2"/>
@@ -20185,7 +20227,7 @@
       <c r="BD13" s="2"/>
     </row>
     <row r="14" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="86"/>
+      <c r="A14" s="106"/>
       <c r="B14" s="52"/>
       <c r="C14" s="44">
         <f>SUM(C12+C13)</f>
@@ -20257,11 +20299,11 @@
       </c>
       <c r="T14" s="44">
         <f t="shared" si="4"/>
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="V14" s="44">
         <f t="shared" si="4"/>
@@ -20331,9 +20373,9 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="117"/>
-      <c r="AN14" s="124"/>
-      <c r="AO14" s="131"/>
+      <c r="AM14" s="129"/>
+      <c r="AN14" s="136"/>
+      <c r="AO14" s="143"/>
       <c r="AP14" s="13"/>
       <c r="AQ14" s="13"/>
       <c r="AR14" s="13"/>
@@ -20351,7 +20393,7 @@
       <c r="BD14" s="13"/>
     </row>
     <row r="15" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="87" t="str">
+      <c r="A15" s="107" t="str">
         <f>Drivers!AQ13</f>
         <v>Gehr (1)</v>
       </c>
@@ -20429,11 +20471,11 @@
       </c>
       <c r="T15" s="38">
         <f>Drivers!T24</f>
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="U15" s="38">
         <f>Drivers!U24</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="V15" s="38">
         <f>Drivers!V24</f>
@@ -20503,17 +20545,17 @@
         <f>Drivers!AL24</f>
         <v>0</v>
       </c>
-      <c r="AM15" s="118">
+      <c r="AM15" s="130">
         <f>SUM(C17:AL17)</f>
-        <v>1027</v>
-      </c>
-      <c r="AN15" s="125">
+        <v>1106</v>
+      </c>
+      <c r="AN15" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>3</v>
       </c>
-      <c r="AO15" s="129">
+      <c r="AO15" s="141">
         <f t="shared" ref="AO15" si="5">AVERAGE(C17:AL17)</f>
-        <v>28.527777777777779</v>
+        <v>30.722222222222221</v>
       </c>
       <c r="AP15" s="2"/>
       <c r="AQ15" s="13"/>
@@ -20532,7 +20574,7 @@
       <c r="BD15" s="2"/>
     </row>
     <row r="16" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A16" s="85"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="78" t="str">
         <f>Drivers!AR14</f>
         <v>Gibbs</v>
@@ -20607,11 +20649,11 @@
       </c>
       <c r="T16" s="26">
         <f>Drivers!T39</f>
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="U16" s="26">
         <f>Drivers!U39</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="V16" s="26">
         <f>Drivers!V39</f>
@@ -20681,9 +20723,9 @@
         <f>Drivers!AL39</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="117"/>
-      <c r="AN16" s="124"/>
-      <c r="AO16" s="130"/>
+      <c r="AM16" s="129"/>
+      <c r="AN16" s="136"/>
+      <c r="AO16" s="142"/>
       <c r="AP16" s="2"/>
       <c r="AQ16" s="13"/>
       <c r="AR16" s="2"/>
@@ -20701,7 +20743,7 @@
       <c r="BD16" s="2"/>
     </row>
     <row r="17" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="86"/>
+      <c r="A17" s="106"/>
       <c r="B17" s="52"/>
       <c r="C17" s="44">
         <f>SUM(C15+C16)</f>
@@ -20773,11 +20815,11 @@
       </c>
       <c r="T17" s="44">
         <f t="shared" si="6"/>
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="V17" s="44">
         <f t="shared" si="6"/>
@@ -20847,9 +20889,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM17" s="119"/>
-      <c r="AN17" s="126"/>
-      <c r="AO17" s="131"/>
+      <c r="AM17" s="131"/>
+      <c r="AN17" s="138"/>
+      <c r="AO17" s="143"/>
       <c r="AP17" s="13"/>
       <c r="AQ17" s="13"/>
       <c r="AR17" s="13"/>
@@ -20867,7 +20909,7 @@
       <c r="BD17" s="13"/>
     </row>
     <row r="18" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="87" t="str">
+      <c r="A18" s="107" t="str">
         <f>Drivers!AQ16</f>
         <v>Devin  (1)</v>
       </c>
@@ -20945,11 +20987,11 @@
       </c>
       <c r="T18" s="38">
         <f>Drivers!T14</f>
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="U18" s="38">
         <f>Drivers!U14</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="V18" s="38">
         <f>Drivers!V14</f>
@@ -21019,17 +21061,17 @@
         <f>Drivers!AL14</f>
         <v>0</v>
       </c>
-      <c r="AM18" s="118">
+      <c r="AM18" s="130">
         <f>SUM(C20:AL20)</f>
-        <v>1182</v>
-      </c>
-      <c r="AN18" s="127">
+        <v>1226</v>
+      </c>
+      <c r="AN18" s="139">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>2</v>
       </c>
-      <c r="AO18" s="129">
+      <c r="AO18" s="141">
         <f t="shared" ref="AO18" si="7">AVERAGE(C20:AL20)</f>
-        <v>32.833333333333336</v>
+        <v>34.055555555555557</v>
       </c>
       <c r="AP18" s="2"/>
       <c r="AQ18" s="13"/>
@@ -21048,7 +21090,7 @@
       <c r="BD18" s="2"/>
     </row>
     <row r="19" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A19" s="85"/>
+      <c r="A19" s="105"/>
       <c r="B19" s="78" t="str">
         <f>Drivers!AR17</f>
         <v>Hosevar</v>
@@ -21123,11 +21165,11 @@
       </c>
       <c r="T19" s="26">
         <f>Drivers!T42</f>
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="U19" s="26">
         <f>Drivers!U42</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V19" s="26">
         <f>Drivers!V42</f>
@@ -21197,9 +21239,9 @@
         <f>Drivers!AL42</f>
         <v>0</v>
       </c>
-      <c r="AM19" s="117"/>
-      <c r="AN19" s="124"/>
-      <c r="AO19" s="130"/>
+      <c r="AM19" s="129"/>
+      <c r="AN19" s="136"/>
+      <c r="AO19" s="142"/>
       <c r="AP19" s="2"/>
       <c r="AQ19" s="13"/>
       <c r="AR19" s="2"/>
@@ -21217,7 +21259,7 @@
       <c r="BD19" s="2"/>
     </row>
     <row r="20" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="86"/>
+      <c r="A20" s="106"/>
       <c r="B20" s="52"/>
       <c r="C20" s="44">
         <f>SUM(C18+C19)</f>
@@ -21289,11 +21331,11 @@
       </c>
       <c r="T20" s="44">
         <f t="shared" si="8"/>
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="V20" s="44">
         <f t="shared" si="8"/>
@@ -21363,9 +21405,9 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AM20" s="119"/>
-      <c r="AN20" s="124"/>
-      <c r="AO20" s="131"/>
+      <c r="AM20" s="131"/>
+      <c r="AN20" s="136"/>
+      <c r="AO20" s="143"/>
       <c r="AP20" s="13"/>
       <c r="AQ20" s="13"/>
       <c r="AR20" s="13"/>
@@ -21383,7 +21425,7 @@
       <c r="BD20" s="13"/>
     </row>
     <row r="21" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87" t="str">
+      <c r="A21" s="107" t="str">
         <f>Drivers!AQ19</f>
         <v>Jack-n-Bob</v>
       </c>
@@ -21461,11 +21503,11 @@
       </c>
       <c r="T21" s="38">
         <f>Drivers!T45</f>
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="U21" s="38">
         <f>Drivers!U45</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V21" s="38">
         <f>Drivers!V45</f>
@@ -21535,17 +21577,17 @@
         <f>Drivers!AL45</f>
         <v>0</v>
       </c>
-      <c r="AM21" s="118">
+      <c r="AM21" s="130">
         <f>SUM(C23:AL23)</f>
-        <v>559</v>
-      </c>
-      <c r="AN21" s="125">
+        <v>609</v>
+      </c>
+      <c r="AN21" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>8</v>
       </c>
-      <c r="AO21" s="129">
+      <c r="AO21" s="141">
         <f t="shared" ref="AO21" si="9">AVERAGE(C23:AL23)</f>
-        <v>15.527777777777779</v>
+        <v>16.916666666666668</v>
       </c>
       <c r="AP21" s="2"/>
       <c r="AQ21" s="13"/>
@@ -21564,7 +21606,7 @@
       <c r="BD21" s="2"/>
     </row>
     <row r="22" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A22" s="85"/>
+      <c r="A22" s="105"/>
       <c r="B22" s="49" t="str">
         <f>Drivers!AR20</f>
         <v>E. Jones</v>
@@ -21639,11 +21681,11 @@
       </c>
       <c r="T22" s="26">
         <f>Drivers!T32</f>
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="U22" s="26">
         <f>Drivers!U32</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="V22" s="26">
         <f>Drivers!V32</f>
@@ -21713,9 +21755,9 @@
         <f>Drivers!AL32</f>
         <v>0</v>
       </c>
-      <c r="AM22" s="117"/>
-      <c r="AN22" s="124"/>
-      <c r="AO22" s="130"/>
+      <c r="AM22" s="129"/>
+      <c r="AN22" s="136"/>
+      <c r="AO22" s="142"/>
       <c r="AP22" s="2"/>
       <c r="AQ22" s="13"/>
       <c r="AR22" s="2"/>
@@ -21733,7 +21775,7 @@
       <c r="BD22" s="2"/>
     </row>
     <row r="23" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="86"/>
+      <c r="A23" s="106"/>
       <c r="B23" s="51"/>
       <c r="C23" s="44">
         <f>SUM(C21+C22)</f>
@@ -21805,11 +21847,11 @@
       </c>
       <c r="T23" s="44">
         <f t="shared" si="10"/>
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V23" s="44">
         <f t="shared" si="10"/>
@@ -21879,9 +21921,9 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AM23" s="119"/>
-      <c r="AN23" s="126"/>
-      <c r="AO23" s="131"/>
+      <c r="AM23" s="131"/>
+      <c r="AN23" s="138"/>
+      <c r="AO23" s="143"/>
       <c r="AP23" s="13"/>
       <c r="AQ23" s="13"/>
       <c r="AR23" s="13"/>
@@ -21899,7 +21941,7 @@
       <c r="BD23" s="13"/>
     </row>
     <row r="24" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87" t="str">
+      <c r="A24" s="107" t="str">
         <f>Drivers!AQ22</f>
         <v>Ray (2)</v>
       </c>
@@ -21977,11 +22019,11 @@
       </c>
       <c r="T24" s="38">
         <f>Drivers!T15</f>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="U24" s="38">
         <f>Drivers!U15</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V24" s="38">
         <f>Drivers!V15</f>
@@ -22051,17 +22093,17 @@
         <f>Drivers!AL15</f>
         <v>0</v>
       </c>
-      <c r="AM24" s="116">
+      <c r="AM24" s="128">
         <f>SUM(C26:AL26)</f>
-        <v>941</v>
-      </c>
-      <c r="AN24" s="127">
+        <v>1036</v>
+      </c>
+      <c r="AN24" s="139">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>6</v>
       </c>
-      <c r="AO24" s="129">
+      <c r="AO24" s="141">
         <f t="shared" ref="AO24" si="11">AVERAGE(C26:AL26)</f>
-        <v>26.138888888888889</v>
+        <v>28.777777777777779</v>
       </c>
       <c r="AP24" s="2"/>
       <c r="AQ24" s="13"/>
@@ -22080,7 +22122,7 @@
       <c r="BD24" s="2"/>
     </row>
     <row r="25" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="78" t="str">
         <f>Drivers!AR23</f>
         <v>Van Gisbergen</v>
@@ -22155,11 +22197,11 @@
       </c>
       <c r="T25" s="26">
         <f>Drivers!T46</f>
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="U25" s="26">
         <f>Drivers!U46</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V25" s="26">
         <f>Drivers!V46</f>
@@ -22229,9 +22271,9 @@
         <f>Drivers!AL46</f>
         <v>0</v>
       </c>
-      <c r="AM25" s="117"/>
-      <c r="AN25" s="124"/>
-      <c r="AO25" s="130"/>
+      <c r="AM25" s="129"/>
+      <c r="AN25" s="136"/>
+      <c r="AO25" s="142"/>
       <c r="AP25" s="2"/>
       <c r="AQ25" s="13"/>
       <c r="AR25" s="2"/>
@@ -22249,7 +22291,7 @@
       <c r="BD25" s="2"/>
     </row>
     <row r="26" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="86"/>
+      <c r="A26" s="106"/>
       <c r="B26" s="52"/>
       <c r="C26" s="44">
         <f>SUM(C24+C25)</f>
@@ -22321,11 +22363,11 @@
       </c>
       <c r="T26" s="44">
         <f t="shared" si="12"/>
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="V26" s="44">
         <f t="shared" si="12"/>
@@ -22395,9 +22437,9 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AM26" s="117"/>
-      <c r="AN26" s="124"/>
-      <c r="AO26" s="131"/>
+      <c r="AM26" s="129"/>
+      <c r="AN26" s="136"/>
+      <c r="AO26" s="143"/>
       <c r="AP26" s="13"/>
       <c r="AQ26" s="13"/>
       <c r="AR26" s="13"/>
@@ -22415,7 +22457,7 @@
       <c r="BD26" s="13"/>
     </row>
     <row r="27" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87" t="str">
+      <c r="A27" s="107" t="str">
         <f>Drivers!AQ25</f>
         <v>Rob</v>
       </c>
@@ -22493,11 +22535,11 @@
       </c>
       <c r="T27" s="38">
         <f>Drivers!T12</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="U27" s="38">
         <f>Drivers!U12</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V27" s="38">
         <f>Drivers!V12</f>
@@ -22567,17 +22609,17 @@
         <f>Drivers!AL12</f>
         <v>0</v>
       </c>
-      <c r="AM27" s="118">
+      <c r="AM27" s="130">
         <f>SUM(C29:AL29)</f>
-        <v>1272</v>
-      </c>
-      <c r="AN27" s="125">
+        <v>1294</v>
+      </c>
+      <c r="AN27" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>1</v>
       </c>
-      <c r="AO27" s="129">
+      <c r="AO27" s="141">
         <f t="shared" ref="AO27" si="13">AVERAGE(C29:AL29)</f>
-        <v>35.333333333333336</v>
+        <v>35.944444444444443</v>
       </c>
       <c r="AP27" s="2"/>
       <c r="AQ27" s="13"/>
@@ -22596,7 +22638,7 @@
       <c r="BD27" s="2"/>
     </row>
     <row r="28" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A28" s="85"/>
+      <c r="A28" s="105"/>
       <c r="B28" s="49" t="str">
         <f>Drivers!AR26</f>
         <v>Reddick</v>
@@ -22675,7 +22717,7 @@
       </c>
       <c r="U28" s="26">
         <f>Drivers!U34</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V28" s="26">
         <f>Drivers!V34</f>
@@ -22745,9 +22787,9 @@
         <f>Drivers!AL34</f>
         <v>0</v>
       </c>
-      <c r="AM28" s="117"/>
-      <c r="AN28" s="124"/>
-      <c r="AO28" s="130"/>
+      <c r="AM28" s="129"/>
+      <c r="AN28" s="136"/>
+      <c r="AO28" s="142"/>
       <c r="AP28" s="2"/>
       <c r="AQ28" s="13"/>
       <c r="AR28" s="2"/>
@@ -22765,7 +22807,7 @@
       <c r="BD28" s="2"/>
     </row>
     <row r="29" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="86"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="52"/>
       <c r="C29" s="44">
         <f>SUM(C27+C28)</f>
@@ -22837,11 +22879,11 @@
       </c>
       <c r="T29" s="44">
         <f t="shared" si="14"/>
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="U29" s="44">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V29" s="44">
         <f t="shared" si="14"/>
@@ -22911,9 +22953,9 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AM29" s="117"/>
-      <c r="AN29" s="126"/>
-      <c r="AO29" s="131"/>
+      <c r="AM29" s="129"/>
+      <c r="AN29" s="138"/>
+      <c r="AO29" s="143"/>
       <c r="AP29" s="13"/>
       <c r="AQ29" s="13"/>
       <c r="AR29" s="13"/>
@@ -22931,7 +22973,7 @@
       <c r="BD29" s="13"/>
     </row>
     <row r="30" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="103">
+      <c r="A30" s="119">
         <f>Drivers!AQ28</f>
         <v>9</v>
       </c>
@@ -22975,15 +23017,15 @@
       <c r="AJ30" s="40"/>
       <c r="AK30" s="40"/>
       <c r="AL30" s="43"/>
-      <c r="AM30" s="118">
+      <c r="AM30" s="130">
         <f>SUM(C32:AL32)</f>
         <v>0</v>
       </c>
-      <c r="AN30" s="125">
+      <c r="AN30" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>9</v>
       </c>
-      <c r="AO30" s="129">
+      <c r="AO30" s="141">
         <f t="shared" ref="AO30" si="15">AVERAGE(C32:AL32)</f>
         <v>0</v>
       </c>
@@ -23004,7 +23046,7 @@
       <c r="BD30" s="2"/>
     </row>
     <row r="31" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A31" s="85"/>
+      <c r="A31" s="105"/>
       <c r="B31" s="49" t="str">
         <f>Drivers!AR29</f>
         <v>B</v>
@@ -23045,9 +23087,9 @@
       <c r="AJ31" s="33"/>
       <c r="AK31" s="33"/>
       <c r="AL31" s="30"/>
-      <c r="AM31" s="117"/>
-      <c r="AN31" s="124"/>
-      <c r="AO31" s="130"/>
+      <c r="AM31" s="129"/>
+      <c r="AN31" s="136"/>
+      <c r="AO31" s="142"/>
       <c r="AP31" s="2"/>
       <c r="AQ31" s="13"/>
       <c r="AR31" s="2"/>
@@ -23065,7 +23107,7 @@
       <c r="BD31" s="2"/>
     </row>
     <row r="32" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A32" s="85"/>
+      <c r="A32" s="105"/>
       <c r="B32" s="52"/>
       <c r="C32" s="44">
         <f>SUM(C30+C31)</f>
@@ -23211,9 +23253,9 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AM32" s="119"/>
-      <c r="AN32" s="126"/>
-      <c r="AO32" s="131"/>
+      <c r="AM32" s="131"/>
+      <c r="AN32" s="138"/>
+      <c r="AO32" s="143"/>
       <c r="AP32" s="13"/>
       <c r="AQ32" s="13"/>
       <c r="AR32" s="13"/>
@@ -23231,7 +23273,7 @@
       <c r="BD32" s="13"/>
     </row>
     <row r="33" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="87">
+      <c r="A33" s="107">
         <f>Drivers!AQ31</f>
         <v>10</v>
       </c>
@@ -23275,15 +23317,15 @@
       <c r="AJ33" s="33"/>
       <c r="AK33" s="33"/>
       <c r="AL33" s="30"/>
-      <c r="AM33" s="116">
+      <c r="AM33" s="128">
         <f>SUM(C35:AL35)</f>
         <v>0</v>
       </c>
-      <c r="AN33" s="125">
+      <c r="AN33" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>9</v>
       </c>
-      <c r="AO33" s="132"/>
+      <c r="AO33" s="144"/>
       <c r="AP33" s="2"/>
       <c r="AQ33" s="13"/>
       <c r="AR33" s="2"/>
@@ -23301,7 +23343,7 @@
       <c r="BD33" s="2"/>
     </row>
     <row r="34" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A34" s="85"/>
+      <c r="A34" s="105"/>
       <c r="B34" s="49" t="str">
         <f>Drivers!AR32</f>
         <v>B</v>
@@ -23342,9 +23384,9 @@
       <c r="AJ34" s="33"/>
       <c r="AK34" s="33"/>
       <c r="AL34" s="30"/>
-      <c r="AM34" s="117"/>
-      <c r="AN34" s="124"/>
-      <c r="AO34" s="124"/>
+      <c r="AM34" s="129"/>
+      <c r="AN34" s="136"/>
+      <c r="AO34" s="136"/>
       <c r="AP34" s="2"/>
       <c r="AQ34" s="13"/>
       <c r="AR34" s="2"/>
@@ -23362,7 +23404,7 @@
       <c r="BD34" s="2"/>
     </row>
     <row r="35" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="86"/>
+      <c r="A35" s="106"/>
       <c r="B35" s="54"/>
       <c r="C35" s="35">
         <f>SUM(C33+C34)</f>
@@ -23508,9 +23550,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AM35" s="122"/>
-      <c r="AN35" s="128"/>
-      <c r="AO35" s="128"/>
+      <c r="AM35" s="134"/>
+      <c r="AN35" s="140"/>
+      <c r="AO35" s="140"/>
       <c r="AP35" s="13"/>
       <c r="AQ35" s="13"/>
       <c r="AR35" s="13"/>
@@ -28311,28 +28353,28 @@
     </row>
     <row r="121" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A121" s="21"/>
-      <c r="C121" s="120"/>
-      <c r="D121" s="121"/>
-      <c r="E121" s="121"/>
-      <c r="F121" s="121"/>
-      <c r="G121" s="121"/>
-      <c r="H121" s="121"/>
-      <c r="I121" s="121"/>
-      <c r="J121" s="121"/>
-      <c r="K121" s="121"/>
-      <c r="L121" s="121"/>
+      <c r="C121" s="132"/>
+      <c r="D121" s="133"/>
+      <c r="E121" s="133"/>
+      <c r="F121" s="133"/>
+      <c r="G121" s="133"/>
+      <c r="H121" s="133"/>
+      <c r="I121" s="133"/>
+      <c r="J121" s="133"/>
+      <c r="K121" s="133"/>
+      <c r="L121" s="133"/>
     </row>
     <row r="122" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="C122" s="121"/>
-      <c r="D122" s="121"/>
-      <c r="E122" s="121"/>
-      <c r="F122" s="121"/>
-      <c r="G122" s="121"/>
-      <c r="H122" s="121"/>
-      <c r="I122" s="121"/>
-      <c r="J122" s="121"/>
-      <c r="K122" s="121"/>
-      <c r="L122" s="121"/>
+      <c r="C122" s="133"/>
+      <c r="D122" s="133"/>
+      <c r="E122" s="133"/>
+      <c r="F122" s="133"/>
+      <c r="G122" s="133"/>
+      <c r="H122" s="133"/>
+      <c r="I122" s="133"/>
+      <c r="J122" s="133"/>
+      <c r="K122" s="133"/>
+      <c r="L122" s="133"/>
     </row>
     <row r="123" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A123" s="21"/>
@@ -28585,10 +28627,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:56" ht="22" x14ac:dyDescent="0.25">
-      <c r="A1" s="81">
+      <c r="A1" s="101">
         <v>2025</v>
       </c>
-      <c r="B1" s="82"/>
+      <c r="B1" s="102"/>
       <c r="C1" s="146" t="s">
         <v>75</v>
       </c>
@@ -28633,8 +28675,8 @@
       <c r="AP1" s="48"/>
     </row>
     <row r="2" spans="1:56" ht="22.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
+      <c r="A2" s="103"/>
+      <c r="B2" s="103"/>
       <c r="C2" s="148"/>
       <c r="D2" s="148"/>
       <c r="E2" s="148"/>
@@ -28677,263 +28719,263 @@
       <c r="AP2" s="48"/>
     </row>
     <row r="3" spans="1:56" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="113" t="s">
+      <c r="A3" s="125" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="110" t="s">
+      <c r="B3" s="89" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="87" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="100" t="s">
+      <c r="D3" s="84" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="97" t="s">
+      <c r="E3" s="87" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="100" t="s">
+      <c r="F3" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="G3" s="97" t="s">
+      <c r="G3" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="100" t="s">
+      <c r="H3" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="I3" s="97" t="s">
+      <c r="I3" s="87" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="100" t="s">
+      <c r="J3" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="97" t="s">
+      <c r="K3" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="100" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="97" t="s">
+      <c r="L3" s="84" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="87" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="97" t="s">
+      <c r="N3" s="87" t="s">
         <v>2</v>
       </c>
-      <c r="O3" s="97" t="s">
+      <c r="O3" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="P3" s="97" t="s">
+      <c r="P3" s="87" t="s">
         <v>4</v>
       </c>
-      <c r="Q3" s="97" t="s">
+      <c r="Q3" s="87" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="97" t="s">
+      <c r="R3" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="97" t="s">
+      <c r="S3" s="87" t="s">
         <v>7</v>
       </c>
-      <c r="T3" s="97" t="s">
+      <c r="T3" s="87" t="s">
         <v>8</v>
       </c>
-      <c r="U3" s="97" t="s">
+      <c r="U3" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="V3" s="97" t="s">
+      <c r="V3" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="W3" s="97" t="s">
+      <c r="W3" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="X3" s="97" t="s">
+      <c r="X3" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="Y3" s="97" t="s">
+      <c r="Y3" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="Z3" s="97" t="s">
+      <c r="Z3" s="87" t="s">
         <v>14</v>
       </c>
-      <c r="AA3" s="97" t="s">
+      <c r="AA3" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="AB3" s="97" t="s">
+      <c r="AB3" s="87" t="s">
         <v>16</v>
       </c>
-      <c r="AC3" s="100" t="s">
+      <c r="AC3" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="AD3" s="97" t="s">
+      <c r="AD3" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="AE3" s="97" t="s">
+      <c r="AE3" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="AF3" s="97" t="s">
+      <c r="AF3" s="87" t="s">
         <v>22</v>
       </c>
-      <c r="AG3" s="97" t="s">
+      <c r="AG3" s="87" t="s">
         <v>23</v>
       </c>
-      <c r="AH3" s="97" t="s">
+      <c r="AH3" s="87" t="s">
         <v>24</v>
       </c>
-      <c r="AI3" s="97" t="s">
+      <c r="AI3" s="87" t="s">
         <v>25</v>
       </c>
-      <c r="AJ3" s="97" t="s">
+      <c r="AJ3" s="87" t="s">
         <v>26</v>
       </c>
-      <c r="AK3" s="97" t="s">
+      <c r="AK3" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="AL3" s="107" t="s">
+      <c r="AL3" s="91" t="s">
         <v>28</v>
       </c>
-      <c r="AM3" s="88" t="s">
+      <c r="AM3" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="AN3" s="91" t="s">
+      <c r="AN3" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="AO3" s="94" t="s">
+      <c r="AO3" s="114" t="s">
         <v>41</v>
       </c>
       <c r="AP3" s="47"/>
-      <c r="AQ3" s="104"/>
-      <c r="AR3" s="104"/>
-      <c r="AS3" s="104"/>
-      <c r="AT3" s="104"/>
-      <c r="AU3" s="104"/>
-      <c r="AV3" s="104"/>
-      <c r="AW3" s="104"/>
-      <c r="AX3" s="104"/>
-      <c r="AY3" s="104"/>
-      <c r="AZ3" s="104"/>
-      <c r="BA3" s="104"/>
-      <c r="BB3" s="104"/>
-      <c r="BC3" s="104"/>
-      <c r="BD3" s="104"/>
+      <c r="AQ3" s="120"/>
+      <c r="AR3" s="120"/>
+      <c r="AS3" s="120"/>
+      <c r="AT3" s="120"/>
+      <c r="AU3" s="120"/>
+      <c r="AV3" s="120"/>
+      <c r="AW3" s="120"/>
+      <c r="AX3" s="120"/>
+      <c r="AY3" s="120"/>
+      <c r="AZ3" s="120"/>
+      <c r="BA3" s="120"/>
+      <c r="BB3" s="120"/>
+      <c r="BC3" s="120"/>
+      <c r="BD3" s="120"/>
     </row>
     <row r="4" spans="1:56" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="114"/>
-      <c r="B4" s="111"/>
-      <c r="C4" s="98"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="98"/>
-      <c r="L4" s="101"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98"/>
-      <c r="W4" s="98"/>
-      <c r="X4" s="98"/>
-      <c r="Y4" s="98"/>
-      <c r="Z4" s="98"/>
-      <c r="AA4" s="98"/>
-      <c r="AB4" s="98"/>
-      <c r="AC4" s="101"/>
-      <c r="AD4" s="98"/>
-      <c r="AE4" s="98"/>
-      <c r="AF4" s="98"/>
-      <c r="AG4" s="98"/>
-      <c r="AH4" s="98"/>
-      <c r="AI4" s="98"/>
-      <c r="AJ4" s="98"/>
-      <c r="AK4" s="98"/>
-      <c r="AL4" s="108"/>
-      <c r="AM4" s="89"/>
-      <c r="AN4" s="92"/>
-      <c r="AO4" s="95"/>
+      <c r="A4" s="126"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="88"/>
+      <c r="T4" s="88"/>
+      <c r="U4" s="88"/>
+      <c r="V4" s="88"/>
+      <c r="W4" s="88"/>
+      <c r="X4" s="88"/>
+      <c r="Y4" s="88"/>
+      <c r="Z4" s="88"/>
+      <c r="AA4" s="88"/>
+      <c r="AB4" s="88"/>
+      <c r="AC4" s="85"/>
+      <c r="AD4" s="88"/>
+      <c r="AE4" s="88"/>
+      <c r="AF4" s="88"/>
+      <c r="AG4" s="88"/>
+      <c r="AH4" s="88"/>
+      <c r="AI4" s="88"/>
+      <c r="AJ4" s="88"/>
+      <c r="AK4" s="88"/>
+      <c r="AL4" s="92"/>
+      <c r="AM4" s="109"/>
+      <c r="AN4" s="112"/>
+      <c r="AO4" s="115"/>
       <c r="AP4" s="47"/>
-      <c r="AQ4" s="106"/>
-      <c r="AR4" s="105"/>
-      <c r="AS4" s="106"/>
-      <c r="AT4" s="105"/>
-      <c r="AU4" s="106"/>
-      <c r="AV4" s="105"/>
-      <c r="AW4" s="106"/>
-      <c r="AX4" s="105"/>
-      <c r="AY4" s="106"/>
-      <c r="AZ4" s="105"/>
-      <c r="BA4" s="106"/>
-      <c r="BB4" s="105"/>
-      <c r="BC4" s="106"/>
-      <c r="BD4" s="105"/>
+      <c r="AQ4" s="122"/>
+      <c r="AR4" s="121"/>
+      <c r="AS4" s="122"/>
+      <c r="AT4" s="121"/>
+      <c r="AU4" s="122"/>
+      <c r="AV4" s="121"/>
+      <c r="AW4" s="122"/>
+      <c r="AX4" s="121"/>
+      <c r="AY4" s="122"/>
+      <c r="AZ4" s="121"/>
+      <c r="BA4" s="122"/>
+      <c r="BB4" s="121"/>
+      <c r="BC4" s="122"/>
+      <c r="BD4" s="121"/>
     </row>
     <row r="5" spans="1:56" ht="11" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="115"/>
-      <c r="B5" s="112"/>
-      <c r="C5" s="99"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="99"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="99"/>
-      <c r="J5" s="102"/>
-      <c r="K5" s="99"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="99"/>
-      <c r="N5" s="99"/>
-      <c r="O5" s="99"/>
-      <c r="P5" s="99"/>
-      <c r="Q5" s="99"/>
-      <c r="R5" s="99"/>
-      <c r="S5" s="99"/>
-      <c r="T5" s="99"/>
-      <c r="U5" s="99"/>
-      <c r="V5" s="99"/>
-      <c r="W5" s="99"/>
-      <c r="X5" s="99"/>
-      <c r="Y5" s="99"/>
-      <c r="Z5" s="99"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="99"/>
-      <c r="AC5" s="102"/>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="99"/>
-      <c r="AF5" s="99"/>
-      <c r="AG5" s="99"/>
-      <c r="AH5" s="99"/>
-      <c r="AI5" s="99"/>
-      <c r="AJ5" s="99"/>
-      <c r="AK5" s="99"/>
-      <c r="AL5" s="109"/>
-      <c r="AM5" s="90"/>
-      <c r="AN5" s="93"/>
-      <c r="AO5" s="96"/>
+      <c r="A5" s="127"/>
+      <c r="B5" s="124"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="118"/>
+      <c r="K5" s="117"/>
+      <c r="L5" s="118"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="117"/>
+      <c r="W5" s="117"/>
+      <c r="X5" s="117"/>
+      <c r="Y5" s="117"/>
+      <c r="Z5" s="117"/>
+      <c r="AA5" s="117"/>
+      <c r="AB5" s="117"/>
+      <c r="AC5" s="118"/>
+      <c r="AD5" s="117"/>
+      <c r="AE5" s="117"/>
+      <c r="AF5" s="117"/>
+      <c r="AG5" s="117"/>
+      <c r="AH5" s="117"/>
+      <c r="AI5" s="117"/>
+      <c r="AJ5" s="117"/>
+      <c r="AK5" s="117"/>
+      <c r="AL5" s="123"/>
+      <c r="AM5" s="110"/>
+      <c r="AN5" s="113"/>
+      <c r="AO5" s="116"/>
       <c r="AP5" s="47"/>
-      <c r="AQ5" s="106"/>
-      <c r="AR5" s="105"/>
-      <c r="AS5" s="106"/>
-      <c r="AT5" s="105"/>
-      <c r="AU5" s="106"/>
-      <c r="AV5" s="105"/>
-      <c r="AW5" s="106"/>
-      <c r="AX5" s="105"/>
-      <c r="AY5" s="106"/>
-      <c r="AZ5" s="105"/>
-      <c r="BA5" s="106"/>
-      <c r="BB5" s="105"/>
-      <c r="BC5" s="106"/>
-      <c r="BD5" s="105"/>
+      <c r="AQ5" s="122"/>
+      <c r="AR5" s="121"/>
+      <c r="AS5" s="122"/>
+      <c r="AT5" s="121"/>
+      <c r="AU5" s="122"/>
+      <c r="AV5" s="121"/>
+      <c r="AW5" s="122"/>
+      <c r="AX5" s="121"/>
+      <c r="AY5" s="122"/>
+      <c r="AZ5" s="121"/>
+      <c r="BA5" s="122"/>
+      <c r="BB5" s="121"/>
+      <c r="BC5" s="122"/>
+      <c r="BD5" s="121"/>
     </row>
     <row r="6" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="A6" s="84" t="str">
+      <c r="A6" s="104" t="str">
         <f>Drivers!AT4</f>
         <v>Carole</v>
       </c>
@@ -29011,11 +29053,11 @@
       </c>
       <c r="T6" s="25">
         <f>Drivers!T12</f>
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="U6" s="25">
         <f>Drivers!U12</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="V6" s="25">
         <f>Drivers!V12</f>
@@ -29085,21 +29127,21 @@
         <f>Drivers!AL12</f>
         <v>0</v>
       </c>
-      <c r="AM6" s="116">
+      <c r="AM6" s="128">
         <f>SUM(C8:AL8)</f>
-        <v>1272</v>
-      </c>
-      <c r="AN6" s="123">
+        <v>1294</v>
+      </c>
+      <c r="AN6" s="135">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>1</v>
       </c>
-      <c r="AO6" s="129">
+      <c r="AO6" s="141">
         <f>AVERAGE(C8:AL8)</f>
-        <v>35.333333333333336</v>
+        <v>35.944444444444443</v>
       </c>
     </row>
     <row r="7" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A7" s="85"/>
+      <c r="A7" s="105"/>
       <c r="B7" s="49" t="str">
         <f>Drivers!AU5</f>
         <v>Reddick</v>
@@ -29178,7 +29220,7 @@
       </c>
       <c r="U7" s="26">
         <f>Drivers!U34</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" s="26">
         <f>Drivers!V34</f>
@@ -29248,9 +29290,9 @@
         <f>Drivers!AL34</f>
         <v>0</v>
       </c>
-      <c r="AM7" s="117"/>
-      <c r="AN7" s="124"/>
-      <c r="AO7" s="130"/>
+      <c r="AM7" s="129"/>
+      <c r="AN7" s="136"/>
+      <c r="AO7" s="142"/>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2"/>
       <c r="AR7" s="2"/>
@@ -29268,7 +29310,7 @@
       <c r="BD7" s="2"/>
     </row>
     <row r="8" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="86"/>
+      <c r="A8" s="106"/>
       <c r="B8" s="49"/>
       <c r="C8" s="27">
         <f>SUM(C6+C7)</f>
@@ -29340,11 +29382,11 @@
       </c>
       <c r="T8" s="27">
         <f t="shared" si="0"/>
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="U8" s="27">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="V8" s="27">
         <f t="shared" si="0"/>
@@ -29414,9 +29456,9 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AM8" s="117"/>
-      <c r="AN8" s="124"/>
-      <c r="AO8" s="131"/>
+      <c r="AM8" s="129"/>
+      <c r="AN8" s="136"/>
+      <c r="AO8" s="143"/>
       <c r="AP8" s="13"/>
       <c r="AQ8" s="13"/>
       <c r="AR8" s="13"/>
@@ -29434,7 +29476,7 @@
       <c r="BD8" s="13"/>
     </row>
     <row r="9" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A9" s="87" t="str">
+      <c r="A9" s="107" t="str">
         <f>Drivers!AT7</f>
         <v>Butch</v>
       </c>
@@ -29512,11 +29554,11 @@
       </c>
       <c r="T9" s="38">
         <f>Drivers!T19</f>
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="U9" s="38">
         <f>Drivers!U19</f>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V9" s="38">
         <f>Drivers!V19</f>
@@ -29586,17 +29628,17 @@
         <f>Drivers!AL19</f>
         <v>0</v>
       </c>
-      <c r="AM9" s="118">
+      <c r="AM9" s="130">
         <f>SUM(C11:AL11)</f>
-        <v>868</v>
-      </c>
-      <c r="AN9" s="125">
+        <v>968</v>
+      </c>
+      <c r="AN9" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>6</v>
       </c>
-      <c r="AO9" s="129">
+      <c r="AO9" s="141">
         <f t="shared" ref="AO9" si="1">AVERAGE(C11:AL11)</f>
-        <v>24.111111111111111</v>
+        <v>26.888888888888889</v>
       </c>
       <c r="AP9" s="2"/>
       <c r="AQ9" s="13"/>
@@ -29615,7 +29657,7 @@
       <c r="BD9" s="2"/>
     </row>
     <row r="10" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="85"/>
+      <c r="A10" s="105"/>
       <c r="B10" s="49" t="str">
         <f>Drivers!AU8</f>
         <v>Van Gisbergen</v>
@@ -29690,11 +29732,11 @@
       </c>
       <c r="T10" s="26">
         <f>Drivers!T46</f>
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="U10" s="26">
         <f>Drivers!U46</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V10" s="26">
         <f>Drivers!V46</f>
@@ -29764,9 +29806,9 @@
         <f>Drivers!AL46</f>
         <v>0</v>
       </c>
-      <c r="AM10" s="117"/>
-      <c r="AN10" s="124"/>
-      <c r="AO10" s="130"/>
+      <c r="AM10" s="129"/>
+      <c r="AN10" s="136"/>
+      <c r="AO10" s="142"/>
       <c r="AP10" s="2"/>
       <c r="AQ10" s="13"/>
       <c r="AR10" s="2"/>
@@ -29784,7 +29826,7 @@
       <c r="BD10" s="2"/>
     </row>
     <row r="11" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="86"/>
+      <c r="A11" s="106"/>
       <c r="B11" s="51"/>
       <c r="C11" s="44">
         <f>SUM(C9+C10)</f>
@@ -29856,11 +29898,11 @@
       </c>
       <c r="T11" s="44">
         <f t="shared" si="2"/>
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="U11" s="44">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="V11" s="44">
         <f t="shared" si="2"/>
@@ -29930,9 +29972,9 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="AM11" s="119"/>
-      <c r="AN11" s="126"/>
-      <c r="AO11" s="131"/>
+      <c r="AM11" s="131"/>
+      <c r="AN11" s="138"/>
+      <c r="AO11" s="143"/>
       <c r="AP11" s="13"/>
       <c r="AQ11" s="13"/>
       <c r="AR11" s="13"/>
@@ -29950,7 +29992,7 @@
       <c r="BD11" s="13"/>
     </row>
     <row r="12" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="87" t="str">
+      <c r="A12" s="107" t="str">
         <f>Drivers!AT10</f>
         <v>Jason</v>
       </c>
@@ -30028,11 +30070,11 @@
       </c>
       <c r="T12" s="38">
         <f>Drivers!T8</f>
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="U12" s="38">
         <f>Drivers!U8</f>
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V12" s="38">
         <f>Drivers!V8</f>
@@ -30102,17 +30144,17 @@
         <f>Drivers!AL8</f>
         <v>0</v>
       </c>
-      <c r="AM12" s="116">
+      <c r="AM12" s="128">
         <f>SUM(C14:AL14)</f>
-        <v>1045</v>
-      </c>
-      <c r="AN12" s="127">
+        <v>1098</v>
+      </c>
+      <c r="AN12" s="139">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>3</v>
       </c>
-      <c r="AO12" s="129">
+      <c r="AO12" s="141">
         <f t="shared" ref="AO12" si="3">AVERAGE(C14:AL14)</f>
-        <v>29.027777777777779</v>
+        <v>30.5</v>
       </c>
       <c r="AP12" s="2"/>
       <c r="AQ12" s="13"/>
@@ -30131,7 +30173,7 @@
       <c r="BD12" s="2"/>
     </row>
     <row r="13" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
+      <c r="A13" s="105"/>
       <c r="B13" s="49" t="str">
         <f>Drivers!AU11</f>
         <v>Buscher</v>
@@ -30206,11 +30248,11 @@
       </c>
       <c r="T13" s="26">
         <f>Drivers!T18</f>
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="U13" s="26">
         <f>Drivers!U18</f>
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V13" s="26">
         <f>Drivers!V18</f>
@@ -30280,9 +30322,9 @@
         <f>Drivers!AL18</f>
         <v>0</v>
       </c>
-      <c r="AM13" s="117"/>
-      <c r="AN13" s="124"/>
-      <c r="AO13" s="130"/>
+      <c r="AM13" s="129"/>
+      <c r="AN13" s="136"/>
+      <c r="AO13" s="142"/>
       <c r="AP13" s="2"/>
       <c r="AQ13" s="13"/>
       <c r="AR13" s="2"/>
@@ -30300,7 +30342,7 @@
       <c r="BD13" s="2"/>
     </row>
     <row r="14" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="86"/>
+      <c r="A14" s="106"/>
       <c r="B14" s="52"/>
       <c r="C14" s="44">
         <f>SUM(C12+C13)</f>
@@ -30372,11 +30414,11 @@
       </c>
       <c r="T14" s="44">
         <f t="shared" si="4"/>
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="U14" s="44">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="V14" s="44">
         <f t="shared" si="4"/>
@@ -30446,9 +30488,9 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="AM14" s="117"/>
-      <c r="AN14" s="124"/>
-      <c r="AO14" s="131"/>
+      <c r="AM14" s="129"/>
+      <c r="AN14" s="136"/>
+      <c r="AO14" s="143"/>
       <c r="AP14" s="13"/>
       <c r="AQ14" s="13"/>
       <c r="AR14" s="13"/>
@@ -30466,7 +30508,7 @@
       <c r="BD14" s="13"/>
     </row>
     <row r="15" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="87" t="str">
+      <c r="A15" s="107" t="str">
         <f>Drivers!AT13</f>
         <v>Shenk</v>
       </c>
@@ -30544,11 +30586,11 @@
       </c>
       <c r="T15" s="38">
         <f>Drivers!T14</f>
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="U15" s="38">
         <f>Drivers!U14</f>
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="V15" s="38">
         <f>Drivers!V14</f>
@@ -30618,17 +30660,17 @@
         <f>Drivers!AL14</f>
         <v>0</v>
       </c>
-      <c r="AM15" s="118">
+      <c r="AM15" s="130">
         <f>SUM(C17:AL17)</f>
-        <v>1123</v>
-      </c>
-      <c r="AN15" s="125">
+        <v>1147</v>
+      </c>
+      <c r="AN15" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>2</v>
       </c>
-      <c r="AO15" s="129">
+      <c r="AO15" s="141">
         <f t="shared" ref="AO15" si="5">AVERAGE(C17:AL17)</f>
-        <v>31.194444444444443</v>
+        <v>31.861111111111111</v>
       </c>
       <c r="AP15" s="2"/>
       <c r="AQ15" s="13"/>
@@ -30647,7 +30689,7 @@
       <c r="BD15" s="2"/>
     </row>
     <row r="16" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A16" s="85"/>
+      <c r="A16" s="105"/>
       <c r="B16" s="49" t="str">
         <f>Drivers!AU14</f>
         <v>Logano</v>
@@ -30722,11 +30764,11 @@
       </c>
       <c r="T16" s="26">
         <f>Drivers!T22</f>
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="U16" s="26">
         <f>Drivers!U22</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="V16" s="26">
         <f>Drivers!V22</f>
@@ -30796,9 +30838,9 @@
         <f>Drivers!AL22</f>
         <v>0</v>
       </c>
-      <c r="AM16" s="117"/>
-      <c r="AN16" s="124"/>
-      <c r="AO16" s="130"/>
+      <c r="AM16" s="129"/>
+      <c r="AN16" s="136"/>
+      <c r="AO16" s="142"/>
       <c r="AP16" s="2"/>
       <c r="AQ16" s="13"/>
       <c r="AR16" s="2"/>
@@ -30816,7 +30858,7 @@
       <c r="BD16" s="2"/>
     </row>
     <row r="17" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="86"/>
+      <c r="A17" s="106"/>
       <c r="B17" s="52"/>
       <c r="C17" s="44">
         <f>SUM(C15+C16)</f>
@@ -30888,11 +30930,11 @@
       </c>
       <c r="T17" s="44">
         <f t="shared" si="6"/>
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="U17" s="44">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="V17" s="44">
         <f t="shared" si="6"/>
@@ -30962,9 +31004,9 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AM17" s="119"/>
-      <c r="AN17" s="126"/>
-      <c r="AO17" s="131"/>
+      <c r="AM17" s="131"/>
+      <c r="AN17" s="138"/>
+      <c r="AO17" s="143"/>
       <c r="AP17" s="13"/>
       <c r="AQ17" s="13"/>
       <c r="AR17" s="13"/>
@@ -30982,7 +31024,7 @@
       <c r="BD17" s="13"/>
     </row>
     <row r="18" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="87" t="str">
+      <c r="A18" s="107" t="str">
         <f>Drivers!AT16</f>
         <v>Sasko</v>
       </c>
@@ -31060,11 +31102,11 @@
       </c>
       <c r="T18" s="38">
         <f>Drivers!T20</f>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="U18" s="38">
         <f>Drivers!U20</f>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V18" s="38">
         <f>Drivers!V20</f>
@@ -31134,17 +31176,17 @@
         <f>Drivers!AL20</f>
         <v>0</v>
       </c>
-      <c r="AM18" s="118">
+      <c r="AM18" s="130">
         <f>SUM(C20:AL20)</f>
-        <v>672</v>
-      </c>
-      <c r="AN18" s="127">
+        <v>722</v>
+      </c>
+      <c r="AN18" s="139">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>7</v>
       </c>
-      <c r="AO18" s="129">
+      <c r="AO18" s="141">
         <f t="shared" ref="AO18" si="7">AVERAGE(C20:AL20)</f>
-        <v>18.666666666666668</v>
+        <v>20.055555555555557</v>
       </c>
       <c r="AP18" s="2"/>
       <c r="AQ18" s="13"/>
@@ -31163,7 +31205,7 @@
       <c r="BD18" s="2"/>
     </row>
     <row r="19" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A19" s="85"/>
+      <c r="A19" s="105"/>
       <c r="B19" s="49" t="str">
         <f>Drivers!AU17</f>
         <v>K. Busch</v>
@@ -31312,9 +31354,9 @@
         <f>Drivers!AL11</f>
         <v>0</v>
       </c>
-      <c r="AM19" s="117"/>
-      <c r="AN19" s="124"/>
-      <c r="AO19" s="130"/>
+      <c r="AM19" s="129"/>
+      <c r="AN19" s="136"/>
+      <c r="AO19" s="142"/>
       <c r="AP19" s="2"/>
       <c r="AQ19" s="13"/>
       <c r="AR19" s="2"/>
@@ -31332,7 +31374,7 @@
       <c r="BD19" s="2"/>
     </row>
     <row r="20" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="86"/>
+      <c r="A20" s="106"/>
       <c r="B20" s="52"/>
       <c r="C20" s="44">
         <f>SUM(C18+C19)</f>
@@ -31404,11 +31446,11 @@
       </c>
       <c r="T20" s="44">
         <f t="shared" si="8"/>
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="U20" s="44">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V20" s="44">
         <f t="shared" si="8"/>
@@ -31478,9 +31520,9 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="AM20" s="119"/>
-      <c r="AN20" s="124"/>
-      <c r="AO20" s="131"/>
+      <c r="AM20" s="131"/>
+      <c r="AN20" s="136"/>
+      <c r="AO20" s="143"/>
       <c r="AP20" s="13"/>
       <c r="AQ20" s="13"/>
       <c r="AR20" s="13"/>
@@ -31498,7 +31540,7 @@
       <c r="BD20" s="13"/>
     </row>
     <row r="21" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87" t="str">
+      <c r="A21" s="107" t="str">
         <f>Drivers!AT19</f>
         <v>Kyle (1)</v>
       </c>
@@ -31576,11 +31618,11 @@
       </c>
       <c r="T21" s="38">
         <f>Drivers!T24</f>
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="U21" s="38">
         <f>Drivers!U24</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="V21" s="38">
         <f>Drivers!V24</f>
@@ -31650,17 +31692,17 @@
         <f>Drivers!AL24</f>
         <v>0</v>
       </c>
-      <c r="AM21" s="118">
+      <c r="AM21" s="130">
         <f>SUM(C23:AL23)</f>
-        <v>910</v>
-      </c>
-      <c r="AN21" s="125">
+        <v>989</v>
+      </c>
+      <c r="AN21" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>5</v>
       </c>
-      <c r="AO21" s="129">
+      <c r="AO21" s="141">
         <f t="shared" ref="AO21" si="9">AVERAGE(C23:AL23)</f>
-        <v>25.277777777777779</v>
+        <v>27.472222222222221</v>
       </c>
       <c r="AP21" s="2"/>
       <c r="AQ21" s="13"/>
@@ -31679,7 +31721,7 @@
       <c r="BD21" s="2"/>
     </row>
     <row r="22" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A22" s="85"/>
+      <c r="A22" s="105"/>
       <c r="B22" s="78" t="str">
         <f>Drivers!AU20</f>
         <v>Gibbs</v>
@@ -31754,11 +31796,11 @@
       </c>
       <c r="T22" s="26">
         <f>Drivers!T39</f>
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="U22" s="26">
         <f>Drivers!U39</f>
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="V22" s="26">
         <f>Drivers!V39</f>
@@ -31828,9 +31870,9 @@
         <f>Drivers!AL39</f>
         <v>0</v>
       </c>
-      <c r="AM22" s="117"/>
-      <c r="AN22" s="124"/>
-      <c r="AO22" s="130"/>
+      <c r="AM22" s="129"/>
+      <c r="AN22" s="136"/>
+      <c r="AO22" s="142"/>
       <c r="AP22" s="2"/>
       <c r="AQ22" s="13"/>
       <c r="AR22" s="2"/>
@@ -31848,7 +31890,7 @@
       <c r="BD22" s="2"/>
     </row>
     <row r="23" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="86"/>
+      <c r="A23" s="106"/>
       <c r="B23" s="51"/>
       <c r="C23" s="44">
         <f>SUM(C21+C22)</f>
@@ -31920,11 +31962,11 @@
       </c>
       <c r="T23" s="44">
         <f t="shared" si="10"/>
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="U23" s="44">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>91</v>
       </c>
       <c r="V23" s="44">
         <f t="shared" si="10"/>
@@ -31994,9 +32036,9 @@
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AM23" s="119"/>
-      <c r="AN23" s="126"/>
-      <c r="AO23" s="131"/>
+      <c r="AM23" s="131"/>
+      <c r="AN23" s="138"/>
+      <c r="AO23" s="143"/>
       <c r="AP23" s="13"/>
       <c r="AQ23" s="13"/>
       <c r="AR23" s="13"/>
@@ -32014,7 +32056,7 @@
       <c r="BD23" s="13"/>
     </row>
     <row r="24" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87" t="str">
+      <c r="A24" s="107" t="str">
         <f>Drivers!AT22</f>
         <v>Burrey (2)</v>
       </c>
@@ -32092,11 +32134,11 @@
       </c>
       <c r="T24" s="38">
         <f>Drivers!T15</f>
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="U24" s="38">
         <f>Drivers!U15</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="V24" s="38">
         <f>Drivers!V15</f>
@@ -32166,17 +32208,17 @@
         <f>Drivers!AL15</f>
         <v>0</v>
       </c>
-      <c r="AM24" s="116">
+      <c r="AM24" s="128">
         <f>SUM(C26:AL26)</f>
-        <v>976</v>
-      </c>
-      <c r="AN24" s="127">
+        <v>1041</v>
+      </c>
+      <c r="AN24" s="139">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>4</v>
       </c>
-      <c r="AO24" s="129">
+      <c r="AO24" s="141">
         <f t="shared" ref="AO24" si="11">AVERAGE(C26:AL26)</f>
-        <v>27.111111111111111</v>
+        <v>28.916666666666668</v>
       </c>
       <c r="AP24" s="2"/>
       <c r="AQ24" s="13"/>
@@ -32195,7 +32237,7 @@
       <c r="BD24" s="2"/>
     </row>
     <row r="25" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A25" s="85"/>
+      <c r="A25" s="105"/>
       <c r="B25" s="79" t="str">
         <f>Drivers!AU23</f>
         <v>Hosevar</v>
@@ -32270,11 +32312,11 @@
       </c>
       <c r="T25" s="26">
         <f>Drivers!T42</f>
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="U25" s="26">
         <f>Drivers!U42</f>
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V25" s="26">
         <f>Drivers!V42</f>
@@ -32344,9 +32386,9 @@
         <f>Drivers!AL42</f>
         <v>0</v>
       </c>
-      <c r="AM25" s="117"/>
-      <c r="AN25" s="124"/>
-      <c r="AO25" s="130"/>
+      <c r="AM25" s="129"/>
+      <c r="AN25" s="136"/>
+      <c r="AO25" s="142"/>
       <c r="AP25" s="2"/>
       <c r="AQ25" s="13"/>
       <c r="AR25" s="2"/>
@@ -32364,7 +32406,7 @@
       <c r="BD25" s="2"/>
     </row>
     <row r="26" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="86"/>
+      <c r="A26" s="106"/>
       <c r="B26" s="52"/>
       <c r="C26" s="44">
         <f>SUM(C24+C25)</f>
@@ -32436,11 +32478,11 @@
       </c>
       <c r="T26" s="44">
         <f t="shared" si="12"/>
-        <v>51</v>
+        <v>65</v>
       </c>
       <c r="U26" s="44">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="V26" s="44">
         <f t="shared" si="12"/>
@@ -32510,9 +32552,9 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="AM26" s="117"/>
-      <c r="AN26" s="124"/>
-      <c r="AO26" s="131"/>
+      <c r="AM26" s="129"/>
+      <c r="AN26" s="136"/>
+      <c r="AO26" s="143"/>
       <c r="AP26" s="13"/>
       <c r="AQ26" s="13"/>
       <c r="AR26" s="13"/>
@@ -32530,7 +32572,7 @@
       <c r="BD26" s="13"/>
     </row>
     <row r="27" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87">
+      <c r="A27" s="107">
         <f>Drivers!AT25</f>
         <v>8</v>
       </c>
@@ -32574,15 +32616,15 @@
       <c r="AJ27" s="58"/>
       <c r="AK27" s="58"/>
       <c r="AL27" s="43"/>
-      <c r="AM27" s="118">
+      <c r="AM27" s="130">
         <f>SUM(C29:AL29)</f>
         <v>0</v>
       </c>
-      <c r="AN27" s="125">
+      <c r="AN27" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>8</v>
       </c>
-      <c r="AO27" s="129">
+      <c r="AO27" s="141">
         <f t="shared" ref="AO27" si="13">AVERAGE(C29:AL29)</f>
         <v>0</v>
       </c>
@@ -32603,7 +32645,7 @@
       <c r="BD27" s="2"/>
     </row>
     <row r="28" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A28" s="85"/>
+      <c r="A28" s="105"/>
       <c r="B28" s="49" t="str">
         <f>Drivers!AU26</f>
         <v>B</v>
@@ -32644,9 +32686,9 @@
       <c r="AJ28" s="55"/>
       <c r="AK28" s="55"/>
       <c r="AL28" s="30"/>
-      <c r="AM28" s="117"/>
-      <c r="AN28" s="124"/>
-      <c r="AO28" s="130"/>
+      <c r="AM28" s="129"/>
+      <c r="AN28" s="136"/>
+      <c r="AO28" s="142"/>
       <c r="AP28" s="2"/>
       <c r="AQ28" s="13"/>
       <c r="AR28" s="2"/>
@@ -32664,7 +32706,7 @@
       <c r="BD28" s="2"/>
     </row>
     <row r="29" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="86"/>
+      <c r="A29" s="106"/>
       <c r="B29" s="52"/>
       <c r="C29" s="44">
         <f>SUM(C27+C28)</f>
@@ -32810,9 +32852,9 @@
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="AM29" s="117"/>
-      <c r="AN29" s="126"/>
-      <c r="AO29" s="131"/>
+      <c r="AM29" s="129"/>
+      <c r="AN29" s="138"/>
+      <c r="AO29" s="143"/>
       <c r="AP29" s="13"/>
       <c r="AQ29" s="13"/>
       <c r="AR29" s="13"/>
@@ -32830,7 +32872,7 @@
       <c r="BD29" s="13"/>
     </row>
     <row r="30" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="103">
+      <c r="A30" s="119">
         <f>Drivers!AT28</f>
         <v>9</v>
       </c>
@@ -32874,15 +32916,15 @@
       <c r="AJ30" s="40"/>
       <c r="AK30" s="40"/>
       <c r="AL30" s="43"/>
-      <c r="AM30" s="118">
+      <c r="AM30" s="130">
         <f>SUM(C32:AL32)</f>
         <v>0</v>
       </c>
-      <c r="AN30" s="125">
+      <c r="AN30" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>8</v>
       </c>
-      <c r="AO30" s="129">
+      <c r="AO30" s="141">
         <f t="shared" ref="AO30" si="15">AVERAGE(C32:AL32)</f>
         <v>0</v>
       </c>
@@ -32903,7 +32945,7 @@
       <c r="BD30" s="2"/>
     </row>
     <row r="31" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A31" s="85"/>
+      <c r="A31" s="105"/>
       <c r="B31" s="49" t="str">
         <f>Drivers!AU29</f>
         <v>B</v>
@@ -32944,9 +32986,9 @@
       <c r="AJ31" s="33"/>
       <c r="AK31" s="33"/>
       <c r="AL31" s="30"/>
-      <c r="AM31" s="117"/>
-      <c r="AN31" s="124"/>
-      <c r="AO31" s="130"/>
+      <c r="AM31" s="129"/>
+      <c r="AN31" s="136"/>
+      <c r="AO31" s="142"/>
       <c r="AP31" s="2"/>
       <c r="AQ31" s="13"/>
       <c r="AR31" s="2"/>
@@ -32964,7 +33006,7 @@
       <c r="BD31" s="2"/>
     </row>
     <row r="32" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A32" s="85"/>
+      <c r="A32" s="105"/>
       <c r="B32" s="52"/>
       <c r="C32" s="44">
         <f>SUM(C30+C31)</f>
@@ -33110,9 +33152,9 @@
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AM32" s="119"/>
-      <c r="AN32" s="126"/>
-      <c r="AO32" s="131"/>
+      <c r="AM32" s="131"/>
+      <c r="AN32" s="138"/>
+      <c r="AO32" s="143"/>
       <c r="AP32" s="13"/>
       <c r="AQ32" s="13"/>
       <c r="AR32" s="13"/>
@@ -33130,7 +33172,7 @@
       <c r="BD32" s="13"/>
     </row>
     <row r="33" spans="1:56" s="1" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="87">
+      <c r="A33" s="107">
         <f>Drivers!AT31</f>
         <v>10</v>
       </c>
@@ -33174,15 +33216,15 @@
       <c r="AJ33" s="33"/>
       <c r="AK33" s="33"/>
       <c r="AL33" s="30"/>
-      <c r="AM33" s="116">
+      <c r="AM33" s="128">
         <f>SUM(C35:AL35)</f>
         <v>0</v>
       </c>
-      <c r="AN33" s="125">
+      <c r="AN33" s="137">
         <f>RANK($AM$6:$AM$35,$AM$6:$AM$35,1&gt;10)</f>
         <v>8</v>
       </c>
-      <c r="AO33" s="132"/>
+      <c r="AO33" s="144"/>
       <c r="AP33" s="2"/>
       <c r="AQ33" s="13"/>
       <c r="AR33" s="2"/>
@@ -33200,7 +33242,7 @@
       <c r="BD33" s="2"/>
     </row>
     <row r="34" spans="1:56" s="1" customFormat="1" ht="13" x14ac:dyDescent="0.3">
-      <c r="A34" s="85"/>
+      <c r="A34" s="105"/>
       <c r="B34" s="49" t="str">
         <f>Drivers!AU32</f>
         <v>B</v>
@@ -33241,9 +33283,9 @@
       <c r="AJ34" s="33"/>
       <c r="AK34" s="33"/>
       <c r="AL34" s="30"/>
-      <c r="AM34" s="117"/>
-      <c r="AN34" s="124"/>
-      <c r="AO34" s="124"/>
+      <c r="AM34" s="129"/>
+      <c r="AN34" s="136"/>
+      <c r="AO34" s="136"/>
       <c r="AP34" s="2"/>
       <c r="AQ34" s="13"/>
       <c r="AR34" s="2"/>
@@ -33261,7 +33303,7 @@
       <c r="BD34" s="2"/>
     </row>
     <row r="35" spans="1:56" s="1" customFormat="1" ht="13.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="86"/>
+      <c r="A35" s="106"/>
       <c r="B35" s="54"/>
       <c r="C35" s="35">
         <f>SUM(C33+C34)</f>
@@ -33407,9 +33449,9 @@
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AM35" s="122"/>
-      <c r="AN35" s="128"/>
-      <c r="AO35" s="128"/>
+      <c r="AM35" s="134"/>
+      <c r="AN35" s="140"/>
+      <c r="AO35" s="140"/>
       <c r="AP35" s="13"/>
       <c r="AQ35" s="13"/>
       <c r="AR35" s="13"/>
@@ -38210,28 +38252,28 @@
     </row>
     <row r="121" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A121" s="21"/>
-      <c r="C121" s="120"/>
-      <c r="D121" s="121"/>
-      <c r="E121" s="121"/>
-      <c r="F121" s="121"/>
-      <c r="G121" s="121"/>
-      <c r="H121" s="121"/>
-      <c r="I121" s="121"/>
-      <c r="J121" s="121"/>
-      <c r="K121" s="121"/>
-      <c r="L121" s="121"/>
+      <c r="C121" s="132"/>
+      <c r="D121" s="133"/>
+      <c r="E121" s="133"/>
+      <c r="F121" s="133"/>
+      <c r="G121" s="133"/>
+      <c r="H121" s="133"/>
+      <c r="I121" s="133"/>
+      <c r="J121" s="133"/>
+      <c r="K121" s="133"/>
+      <c r="L121" s="133"/>
     </row>
     <row r="122" spans="1:56" x14ac:dyDescent="0.25">
-      <c r="C122" s="121"/>
-      <c r="D122" s="121"/>
-      <c r="E122" s="121"/>
-      <c r="F122" s="121"/>
-      <c r="G122" s="121"/>
-      <c r="H122" s="121"/>
-      <c r="I122" s="121"/>
-      <c r="J122" s="121"/>
-      <c r="K122" s="121"/>
-      <c r="L122" s="121"/>
+      <c r="C122" s="133"/>
+      <c r="D122" s="133"/>
+      <c r="E122" s="133"/>
+      <c r="F122" s="133"/>
+      <c r="G122" s="133"/>
+      <c r="H122" s="133"/>
+      <c r="I122" s="133"/>
+      <c r="J122" s="133"/>
+      <c r="K122" s="133"/>
+      <c r="L122" s="133"/>
     </row>
     <row r="123" spans="1:56" x14ac:dyDescent="0.25">
       <c r="A123" s="21"/>
